--- a/results/EVIDENCIAS/10 Revisión final/CHECKLIST_COMPLETADO_2026-09-13.xlsx
+++ b/results/EVIDENCIAS/10 Revisión final/CHECKLIST_COMPLETADO_2026-09-13.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/56DF2B9A7CCB28B8/Email attachments/Documentos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/56df2b9a7ccb28b8/Desktop/ARTICULO DE PSILOCIBINA/gitubn/Rama-de-revisi-n-sistem-tica-/results/EVIDENCIAS/10 Revisión final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{E1C8554C-025E-4E4E-8C6E-5DB9F1AEFEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADAA1D39-0F39-494F-9CF7-19F672A9B8CD}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="8_{E1C8554C-025E-4E4E-8C6E-5DB9F1AEFEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EDD53AF-B479-4621-B4CD-812FA7778DB8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{410CF46D-D88C-4FDB-B3F4-1A2302ECC639}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="467">
   <si>
     <t>RESUMEN</t>
   </si>
@@ -1256,9 +1256,6 @@
     <t>;C]</t>
   </si>
   <si>
-    <t>registradp</t>
-  </si>
-  <si>
     <t>ACTUALIZAR JUSTI</t>
   </si>
   <si>
@@ -1365,6 +1362,135 @@
   </si>
   <si>
     <t>.</t>
+  </si>
+  <si>
+    <t>Evaluación basada en manuscrito; fase pendiente o parcial.</t>
+  </si>
+  <si>
+    <t>Código y corpus disponibles; formularios y datos clínicos finales pendientes.</t>
+  </si>
+  <si>
+    <t>Corpus, tablas, estrategias, pipeline y repositorio disponibles; datos clínicos pendientes.</t>
+  </si>
+  <si>
+    <t>Contribuciones CRediT pendientes.</t>
+  </si>
+  <si>
+    <t>Ausencia de financiamiento externo y conflicto de intereses declarada.</t>
+  </si>
+  <si>
+    <t>Registro PROSPERO CRD420261493650 y versión 1.2 informados.</t>
+  </si>
+  <si>
+    <t>Implicaciones futuras señaladas; no hay implicaciones clínicas finales.</t>
+  </si>
+  <si>
+    <t>Limitaciones del flujo PRISMA y ausencia de extracción clínica reconocidas.</t>
+  </si>
+  <si>
+    <t>Limitaciones de placebo, desenmascaramiento, apoyo y seguimiento discutidas.</t>
+  </si>
+  <si>
+    <t>Discusión provisional; falta discusión de evidencia clínica incluida.</t>
+  </si>
+  <si>
+    <t>No se ha aplicado GRADE a resultados clínicos.</t>
+  </si>
+  <si>
+    <t>No se ha evaluado sesgo de notificación en síntesis.</t>
+  </si>
+  <si>
+    <t>No se han realizado análisis de sensibilidad.</t>
+  </si>
+  <si>
+    <t>No se han explorado causas de heterogeneidad.</t>
+  </si>
+  <si>
+    <t>No hay metaanálisis ni estimaciones agrupadas.</t>
+  </si>
+  <si>
+    <t>No se ha realizado síntesis de estudios incluidos.</t>
+  </si>
+  <si>
+    <t>No hay resultados individuales ni estimaciones de efecto.</t>
+  </si>
+  <si>
+    <t>No hay evaluación de riesgo de sesgo por estudio.</t>
+  </si>
+  <si>
+    <t>No hay tabla de características de estudios incluidos.</t>
+  </si>
+  <si>
+    <t>No se han documentado estudios excluidos con motivos.</t>
+  </si>
+  <si>
+    <t>943 registros, 417 duplicados, 1 retractado y 525 para cribado; etapas posteriores NR.</t>
+  </si>
+  <si>
+    <t>GRADE previsto; aún no aplicado.</t>
+  </si>
+  <si>
+    <t>No se ha evaluado sesgo de notificación.</t>
+  </si>
+  <si>
+    <t>No se han realizado análisis de heterogeneidad.</t>
+  </si>
+  <si>
+    <t>Metaanálisis condicionado a homogeneidad; no ejecutado.</t>
+  </si>
+  <si>
+    <t>Se prevén tablas y síntesis narrativa; tablas finales pendientes.</t>
+  </si>
+  <si>
+    <t>Manejo general descrito; faltan conversiones y datos faltantes.</t>
+  </si>
+  <si>
+    <t>Agrupación prevista por diagnóstico, comparador, dosis, apoyo y seguimiento.</t>
+  </si>
+  <si>
+    <t>Se especifican DM, DME, RR e IC del 95%.</t>
+  </si>
+  <si>
+    <t>Dominios de riesgo descritos; herramienta y evaluaciones pendientes.</t>
+  </si>
+  <si>
+    <t>Variables enumeradas; datos aún no extraídos.</t>
+  </si>
+  <si>
+    <t>Desenlaces clínicos y de seguridad enumerados.</t>
+  </si>
+  <si>
+    <t>Extracción descrita como plan; tabla clínica aún no completada.</t>
+  </si>
+  <si>
+    <t>Dos revisores y consenso planificados; matriz Rayyan pendiente.</t>
+  </si>
+  <si>
+    <t>Estrategias documentadas; falta resolver inconsistencias de fuente y resultados.</t>
+  </si>
+  <si>
+    <t>Fuentes y fecha documentadas; falta armonizar Scopus/Ovid y conteos.</t>
+  </si>
+  <si>
+    <t>PICOS y exclusiones definidos para adultos de 18–65 años.</t>
+  </si>
+  <si>
+    <t>Objetivos general y específicos declarados.</t>
+  </si>
+  <si>
+    <t>Introducción justifica la revisión y separa evidencia bibliométrica y clínica.</t>
+  </si>
+  <si>
+    <t>Resumen estructurado incompleto; la sección Resumen está vacía.</t>
+  </si>
+  <si>
+    <t>Título identifica revisión sistemática en fase de protocolo; no es artículo final.</t>
+  </si>
+  <si>
+    <t>13/09/2026</t>
+  </si>
+  <si>
+    <t>Cribado pendiente de completar en Rayyan</t>
   </si>
 </sst>
 </file>
@@ -4940,10 +5066,10 @@
         <v>134</v>
       </c>
       <c r="O35" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="P35" s="11" t="s">
         <v>414</v>
-      </c>
-      <c r="P35" s="11" t="s">
-        <v>415</v>
       </c>
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
@@ -4995,10 +5121,10 @@
         <v>0.4</v>
       </c>
       <c r="O36" s="62" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="P36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="37" spans="2:18" ht="26.25" customHeight="1">
@@ -5048,10 +5174,10 @@
         <v>0.1</v>
       </c>
       <c r="O37" s="62" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q37" s="2" t="s">
         <v>6</v>
@@ -5104,10 +5230,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q38" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="39" spans="2:18" ht="26.25" customHeight="1">
@@ -5157,10 +5283,10 @@
         <v>0</v>
       </c>
       <c r="P39" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q39" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="40" spans="2:18" ht="26.25" customHeight="1">
@@ -5171,43 +5297,41 @@
         <v>371</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F40" s="52">
+        <v>273</v>
+      </c>
+      <c r="F40" s="52" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G40">
-        <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D40,1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D40,1),Checklist!$J:$J,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J40" s="37">
+        <v>0</v>
+      </c>
+      <c r="J40" s="37" t="e">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D40,1),Checklist!$E:$E,TRUE),G40)</f>
-        <v>0</v>
-      </c>
-      <c r="K40" s="37">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K40" s="37" t="e">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D40,1),Checklist!$F:$F,TRUE),G40)</f>
-        <v>0</v>
-      </c>
-      <c r="L40" s="37">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L40" s="37" t="e">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D40,1),Checklist!$G:$G,TRUE),G40)</f>
-        <v>0</v>
-      </c>
-      <c r="M40" s="37">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M40" s="37" t="e">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D40,1),Checklist!$H:$H,TRUE),G40)</f>
-        <v>0</v>
-      </c>
-      <c r="N40" s="37">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N40" s="37" t="e">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D40,1),Checklist!$I:$I,TRUE),G40)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="41" spans="2:18" ht="26.25" customHeight="1">
@@ -5222,7 +5346,7 @@
       </c>
       <c r="F41" s="52">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41">
         <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D41,1))</f>
@@ -5230,11 +5354,11 @@
       </c>
       <c r="H41">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D41,1),Checklist!$J:$J,0)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J41" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D41,1),Checklist!$E:$E,TRUE),G41)</f>
@@ -5257,7 +5381,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="42" spans="2:18" ht="26.25" customHeight="1">
@@ -5272,7 +5396,7 @@
       </c>
       <c r="F42" s="52">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="G42">
         <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D42,1))</f>
@@ -5280,11 +5404,11 @@
       </c>
       <c r="H42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I42">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D42,1),Checklist!$J:$J,0)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J42" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D42,1),Checklist!$E:$E,TRUE),G42)</f>
@@ -5307,10 +5431,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="43" spans="2:18" ht="26.25" customHeight="1">
@@ -5325,7 +5449,7 @@
       </c>
       <c r="F43" s="52">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="G43">
         <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D43,1))</f>
@@ -5333,11 +5457,11 @@
       </c>
       <c r="H43">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I43">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D43,1),Checklist!$J:$J,0)</f>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J43" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D43,1),Checklist!$E:$E,TRUE),G43)</f>
@@ -5375,7 +5499,7 @@
       </c>
       <c r="F44" s="52">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="G44">
         <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D44,1))</f>
@@ -5383,11 +5507,11 @@
       </c>
       <c r="H44">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I44">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D44,1),Checklist!$J:$J,0)</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J44" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D44,1),Checklist!$E:$E,TRUE),G44)</f>
@@ -5428,7 +5552,7 @@
       </c>
       <c r="F45" s="52">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G45">
         <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D45,1))</f>
@@ -5436,11 +5560,11 @@
       </c>
       <c r="H45">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D45,1),Checklist!$J:$J,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J45" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D45,1),Checklist!$E:$E,TRUE),G45)</f>
@@ -5469,39 +5593,39 @@
     <row r="46" spans="2:18" ht="26.25" customHeight="1">
       <c r="F46" s="52">
         <f t="shared" si="0"/>
-        <v>0.67164179104477617</v>
+        <v>0.83458646616541354</v>
       </c>
       <c r="G46">
         <f>SUM(G36:G45)</f>
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H46">
         <f t="shared" ref="H46:I46" si="2">SUM(H36:H45)</f>
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="I46">
         <f t="shared" si="2"/>
-        <v>44</v>
-      </c>
-      <c r="J46" s="37">
+        <v>23</v>
+      </c>
+      <c r="J46" s="37" t="e">
         <f>_xlfn.PERCENTOF(J36:J45,$G46)</f>
-        <v>2.4350469872857931E-2</v>
-      </c>
-      <c r="K46" s="37">
+        <v>#NUM!</v>
+      </c>
+      <c r="K46" s="37" t="e">
         <f>_xlfn.PERCENTOF(K36:K45,$G46)</f>
-        <v>9.7014925373134324E-3</v>
-      </c>
-      <c r="L46" s="37">
+        <v>#NUM!</v>
+      </c>
+      <c r="L46" s="37" t="e">
         <f>_xlfn.PERCENTOF(L36:L45,$G46)</f>
-        <v>1.0972913211719181E-2</v>
-      </c>
-      <c r="M46" s="37">
+        <v>#NUM!</v>
+      </c>
+      <c r="M46" s="37" t="e">
         <f>_xlfn.PERCENTOF(M36:M45,$G46)</f>
-        <v>0</v>
-      </c>
-      <c r="N46" s="37">
+        <v>#NUM!</v>
+      </c>
+      <c r="N46" s="37" t="e">
         <f>_xlfn.PERCENTOF(N36:N45,$G46)</f>
-        <v>3.7313432835820895E-3</v>
+        <v>#NUM!</v>
       </c>
     </row>
   </sheetData>
@@ -5914,8 +6038,10 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <f>COUNTIF(E3:I3,(NOT(FALSE)))</f>
         <v>2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -5929,8 +6055,11 @@
       <c r="G4" s="33"/>
       <c r="H4" s="33"/>
       <c r="I4" s="33"/>
-      <c r="J4" t="s">
-        <v>366</v>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -5962,8 +6091,10 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <f>COUNTIF(E5:I5,(NOT(FALSE)))</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -5977,8 +6108,11 @@
       <c r="G6" s="33"/>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
-      <c r="J6" t="s">
-        <v>366</v>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="25.5">
@@ -6010,8 +6144,10 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <f t="shared" ref="J7:J8" si="0">COUNTIF(E7:I7,(NOT(FALSE)))</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K7" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="25.5">
@@ -6043,8 +6179,10 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K8" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -6058,8 +6196,11 @@
       <c r="G9" s="33"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
-      <c r="J9" t="s">
-        <v>366</v>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="25.5">
@@ -6091,8 +6232,10 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <f t="shared" ref="J10:J26" si="1">COUNTIF(E10:I10,(NOT(FALSE)))</f>
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K10" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="38.25">
@@ -6124,8 +6267,10 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="25.5">
@@ -6157,8 +6302,10 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="63.75">
@@ -6190,8 +6337,10 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" customHeight="1">
@@ -6223,8 +6372,10 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K14" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="18" customHeight="1">
@@ -6256,8 +6407,10 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K15" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="38.25" customHeight="1">
@@ -6287,11 +6440,13 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="51">
+        <v>1</v>
+      </c>
+      <c r="K16" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="51">
       <c r="A17" t="s">
         <v>373</v>
       </c>
@@ -6320,11 +6475,13 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="38.25">
+        <v>1</v>
+      </c>
+      <c r="K17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="38.25">
       <c r="A18" t="s">
         <v>373</v>
       </c>
@@ -6353,11 +6510,13 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="38.25">
+        <v>2</v>
+      </c>
+      <c r="K18" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="38.25">
       <c r="A19" t="s">
         <v>374</v>
       </c>
@@ -6386,11 +6545,13 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="38.25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="K19" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="38.25" customHeight="1">
       <c r="A20" t="s">
         <v>374</v>
       </c>
@@ -6419,11 +6580,13 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="25.5" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="25.5" customHeight="1">
       <c r="A21" t="s">
         <v>374</v>
       </c>
@@ -6452,11 +6615,13 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="51" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="51" customHeight="1">
       <c r="A22" t="s">
         <v>374</v>
       </c>
@@ -6483,11 +6648,13 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="25.5" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="K22" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="25.5" customHeight="1">
       <c r="A23" t="s">
         <v>374</v>
       </c>
@@ -6514,11 +6681,13 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="25.5" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="25.5" customHeight="1">
       <c r="A24" t="s">
         <v>374</v>
       </c>
@@ -6547,11 +6716,13 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="38.25">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="38.25">
       <c r="A25" t="s">
         <v>373</v>
       </c>
@@ -6580,11 +6751,13 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="25.5">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="25.5">
       <c r="A26" t="s">
         <v>373</v>
       </c>
@@ -6613,11 +6786,13 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>1</v>
+      </c>
+      <c r="K26" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="60"/>
       <c r="C27" s="21" t="s">
         <v>1</v>
@@ -6628,11 +6803,14 @@
       <c r="G27" s="33"/>
       <c r="H27" s="33"/>
       <c r="I27" s="33"/>
-      <c r="J27" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="38.25">
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="38.25">
       <c r="A28" t="s">
         <v>374</v>
       </c>
@@ -6661,11 +6839,13 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <f t="shared" ref="J28:J38" si="2">COUNTIF(E28:I28,(NOT(FALSE)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="25.5" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="K28" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="25.5" customHeight="1">
       <c r="A29" t="s">
         <v>374</v>
       </c>
@@ -6694,11 +6874,13 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="25.5">
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="25.5">
       <c r="A30" t="s">
         <v>374</v>
       </c>
@@ -6727,11 +6909,13 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="38.25">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="38.25">
       <c r="A31" t="s">
         <v>373</v>
       </c>
@@ -6760,11 +6944,13 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="51">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="51">
       <c r="A32" t="s">
         <v>374</v>
       </c>
@@ -6793,8 +6979,10 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="25.5">
@@ -6826,8 +7014,10 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="51" customHeight="1">
@@ -6857,8 +7047,10 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="25.5" customHeight="1">
@@ -6890,8 +7082,10 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K35" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="25.5" customHeight="1">
@@ -6923,8 +7117,10 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="25.5">
@@ -6956,8 +7152,10 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="25.5">
@@ -6989,8 +7187,10 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K38" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -7004,8 +7204,11 @@
       <c r="G39" s="33"/>
       <c r="H39" s="33"/>
       <c r="I39" s="33"/>
-      <c r="J39" t="s">
-        <v>366</v>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="25.5">
@@ -7037,8 +7240,10 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <f t="shared" ref="J40:J43" si="3">COUNTIF(E40:I40,(NOT(FALSE)))</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K40" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1">
@@ -7068,8 +7273,10 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K41" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1">
@@ -7099,8 +7306,10 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K42" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="25.5" customHeight="1">
@@ -7130,8 +7339,10 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K43" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -7145,8 +7356,11 @@
       <c r="G44" s="33"/>
       <c r="H44" s="33"/>
       <c r="I44" s="33"/>
-      <c r="J44" t="s">
-        <v>366</v>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="25.5">
@@ -7178,11 +7392,10 @@
         <v>0</v>
       </c>
       <c r="J45">
-        <f t="shared" ref="J45:J47" si="4">COUNTIF(E45:I45,(NOT(FALSE)))</f>
         <v>2</v>
       </c>
       <c r="K45" t="s">
-        <v>388</v>
+        <v>429</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="25.5">
@@ -7214,8 +7427,10 @@
         <v>0</v>
       </c>
       <c r="J46">
-        <f t="shared" si="4"/>
         <v>2</v>
+      </c>
+      <c r="K46" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="25.5" customHeight="1">
@@ -7245,8 +7460,10 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <f t="shared" si="4"/>
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="K47" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="25.5">
@@ -7278,11 +7495,10 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <f t="shared" ref="J48:J50" si="5">COUNTIF(E48:I48,(NOT(FALSE)))</f>
         <v>2</v>
       </c>
       <c r="K48" t="s">
-        <v>365</v>
+        <v>426</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="38.25">
@@ -7314,8 +7530,10 @@
         <v>0</v>
       </c>
       <c r="J49">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K49" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="51">
@@ -7347,8 +7565,10 @@
         <v>0</v>
       </c>
       <c r="J50">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K50" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -7496,7 +7716,7 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <f t="shared" ref="J56:J59" si="6">COUNTIF(E56:I56,(NOT(FALSE)))</f>
+        <f t="shared" ref="J56:J59" si="0">COUNTIF(E56:I56,(NOT(FALSE)))</f>
         <v>0</v>
       </c>
       <c r="K56" t="s">
@@ -7532,7 +7752,7 @@
         <v>0</v>
       </c>
       <c r="J57">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -7565,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="J58">
-        <f t="shared" ref="J58" si="7">COUNTIF(E58:I58,(NOT(FALSE)))</f>
+        <f t="shared" ref="J58" si="1">COUNTIF(E58:I58,(NOT(FALSE)))</f>
         <v>0</v>
       </c>
     </row>
@@ -7598,7 +7818,7 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7646,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <f t="shared" ref="J61:J62" si="8">COUNTIF(E61:I61,(NOT(FALSE)))</f>
+        <f t="shared" ref="J61:J62" si="2">COUNTIF(E61:I61,(NOT(FALSE)))</f>
         <v>0</v>
       </c>
     </row>
@@ -7679,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -7727,7 +7947,7 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <f t="shared" ref="J64:J65" si="9">COUNTIF(E64:I64,(NOT(FALSE)))</f>
+        <f t="shared" ref="J64:J65" si="3">COUNTIF(E64:I64,(NOT(FALSE)))</f>
         <v>0</v>
       </c>
     </row>
@@ -7760,7 +7980,7 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -7810,7 +8030,7 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <f t="shared" ref="J67:J80" si="10">COUNTIF(E67:I67,(NOT(FALSE)))</f>
+        <f t="shared" ref="J67:J80" si="4">COUNTIF(E67:I67,(NOT(FALSE)))</f>
         <v>1</v>
       </c>
     </row>
@@ -7843,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -7876,11 +8096,11 @@
         <v>0</v>
       </c>
       <c r="J69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="45">
@@ -7912,11 +8132,11 @@
         <v>0</v>
       </c>
       <c r="J70">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="75">
@@ -7948,11 +8168,11 @@
         <v>0</v>
       </c>
       <c r="J71">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="30">
@@ -7984,11 +8204,11 @@
         <v>0</v>
       </c>
       <c r="J72">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="30">
@@ -8020,11 +8240,11 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -8073,7 +8293,7 @@
         <v>0</v>
       </c>
       <c r="J75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -8106,7 +8326,7 @@
         <v>0</v>
       </c>
       <c r="J76">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -8139,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="J77">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K77" t="s">
@@ -8175,7 +8395,7 @@
         <v>0</v>
       </c>
       <c r="J78">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
@@ -8208,11 +8428,11 @@
         <v>0</v>
       </c>
       <c r="J79">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="30">
@@ -8244,11 +8464,11 @@
         <v>0</v>
       </c>
       <c r="J80">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -8299,7 +8519,7 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -8346,11 +8566,11 @@
         <v>0</v>
       </c>
       <c r="J84">
-        <f t="shared" ref="J84:J85" si="11">COUNTIF(E84:I84,(NOT(FALSE)))</f>
+        <f t="shared" ref="J84:J85" si="5">COUNTIF(E84:I84,(NOT(FALSE)))</f>
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="30">
@@ -8382,11 +8602,11 @@
         <v>0</v>
       </c>
       <c r="J85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="30">
@@ -8464,7 +8684,7 @@
         <v>0</v>
       </c>
       <c r="J88">
-        <f t="shared" ref="J88:J121" si="12">COUNTIF(E88:I88,(NOT(FALSE)))</f>
+        <f t="shared" ref="J88:J121" si="6">COUNTIF(E88:I88,(NOT(FALSE)))</f>
         <v>1</v>
       </c>
     </row>
@@ -8493,7 +8713,7 @@
         <v>0</v>
       </c>
       <c r="J89">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -8522,7 +8742,7 @@
         <v>0</v>
       </c>
       <c r="J90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -8551,7 +8771,7 @@
         <v>0</v>
       </c>
       <c r="J91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -8580,11 +8800,11 @@
         <v>0</v>
       </c>
       <c r="J92">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="15" customHeight="1">
@@ -8616,7 +8836,7 @@
         <v>0</v>
       </c>
       <c r="J93">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -8645,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="J94">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -8674,11 +8894,11 @@
         <v>0</v>
       </c>
       <c r="J95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="30">
@@ -8706,11 +8926,11 @@
         <v>0</v>
       </c>
       <c r="J96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="30">
@@ -8738,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="J97">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K97" t="s">
@@ -8774,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="J98">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -8803,7 +9023,7 @@
         <v>0</v>
       </c>
       <c r="J99">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -8832,11 +9052,11 @@
         <v>0</v>
       </c>
       <c r="J100">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K100" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -8864,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="J101">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -8893,11 +9113,11 @@
         <v>0</v>
       </c>
       <c r="J102">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K102" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -8925,7 +9145,7 @@
         <v>0</v>
       </c>
       <c r="J103">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -8954,11 +9174,11 @@
         <v>0</v>
       </c>
       <c r="J104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K104" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -8986,11 +9206,11 @@
         <v>0</v>
       </c>
       <c r="J105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K105" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="30">
@@ -9018,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="J106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -9051,11 +9271,11 @@
         <v>0</v>
       </c>
       <c r="J107">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K107" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="30">
@@ -9083,11 +9303,11 @@
         <v>0</v>
       </c>
       <c r="J108">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K108" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="30">
@@ -9115,11 +9335,11 @@
         <v>0</v>
       </c>
       <c r="J109">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K109" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -9147,7 +9367,7 @@
         <v>0</v>
       </c>
       <c r="J110">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -9176,7 +9396,7 @@
         <v>0</v>
       </c>
       <c r="J111">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -9205,7 +9425,7 @@
         <v>0</v>
       </c>
       <c r="J112">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K112" t="s">
@@ -9237,7 +9457,7 @@
         <v>0</v>
       </c>
       <c r="J113">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -9266,11 +9486,11 @@
         <v>0</v>
       </c>
       <c r="J114">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K114" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="15" customHeight="1">
@@ -9302,7 +9522,7 @@
         <v>0</v>
       </c>
       <c r="J115">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -9331,7 +9551,7 @@
         <v>0</v>
       </c>
       <c r="J116">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -9360,11 +9580,11 @@
         <v>0</v>
       </c>
       <c r="J117">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K117" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="30">
@@ -9396,7 +9616,7 @@
         <v>0</v>
       </c>
       <c r="J118">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -9425,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="J119">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -9454,7 +9674,7 @@
         <v>0</v>
       </c>
       <c r="J120">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -9483,11 +9703,11 @@
         <v>0</v>
       </c>
       <c r="J121">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="15" customHeight="1">
@@ -9567,7 +9787,7 @@
         <v>0</v>
       </c>
       <c r="J124">
-        <f t="shared" ref="J124:J155" si="13">COUNTIF(E124:I124,(NOT(FALSE)))</f>
+        <f t="shared" ref="J124:J155" si="7">COUNTIF(E124:I124,(NOT(FALSE)))</f>
         <v>2</v>
       </c>
     </row>
@@ -9600,7 +9820,7 @@
         <v>1</v>
       </c>
       <c r="J125">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K125" t="s">
@@ -9636,7 +9856,7 @@
         <v>0</v>
       </c>
       <c r="J126">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="K126" t="s">
@@ -9689,7 +9909,7 @@
         <v>1</v>
       </c>
       <c r="J128">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="K128" t="s">
@@ -9725,11 +9945,11 @@
         <v>1</v>
       </c>
       <c r="J129">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="12.75" customHeight="1">
@@ -9761,7 +9981,7 @@
         <v>0</v>
       </c>
       <c r="J130">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="K130" t="s">
@@ -9814,7 +10034,7 @@
         <v>0</v>
       </c>
       <c r="J132">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K132" t="s">
@@ -9850,7 +10070,7 @@
         <v>0</v>
       </c>
       <c r="J133">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K133" t="s">
@@ -9886,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="J134">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="K134" t="s">
@@ -9939,7 +10159,7 @@
         <v>1</v>
       </c>
       <c r="J136">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -9972,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="J137">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -10020,7 +10240,7 @@
         <v>1</v>
       </c>
       <c r="J139">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -10053,7 +10273,7 @@
         <v>0</v>
       </c>
       <c r="J140">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -10086,7 +10306,7 @@
         <v>0</v>
       </c>
       <c r="J141">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -10134,7 +10354,7 @@
         <v>0</v>
       </c>
       <c r="J143">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -10167,7 +10387,7 @@
         <v>0</v>
       </c>
       <c r="J144">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -10200,7 +10420,7 @@
         <v>0</v>
       </c>
       <c r="J145">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -10233,7 +10453,7 @@
         <v>0</v>
       </c>
       <c r="J146">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -10266,11 +10486,11 @@
         <v>0</v>
       </c>
       <c r="J147">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="K147" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="57">
@@ -10302,7 +10522,7 @@
         <v>0</v>
       </c>
       <c r="J148">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -10350,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="J150">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -10381,7 +10601,7 @@
         <v>0</v>
       </c>
       <c r="J151">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -10412,11 +10632,11 @@
         <v>0</v>
       </c>
       <c r="J152">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="K152" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="28.5">
@@ -10446,7 +10666,7 @@
         <v>0</v>
       </c>
       <c r="J153">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K153" t="s">
@@ -10482,7 +10702,7 @@
         <v>0</v>
       </c>
       <c r="J154">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -10515,7 +10735,7 @@
         <v>0</v>
       </c>
       <c r="J155">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -10907,12 +11127,14 @@
         <v>46280</v>
       </c>
       <c r="D26" s="40" t="s">
-        <v>371</v>
+        <v>273</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="F26" s="4"/>
+        <v>465</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="27" spans="3:8">
       <c r="C27" s="39">

--- a/results/EVIDENCIAS/10 Revisión final/CHECKLIST_COMPLETADO_2026-09-13.xlsx
+++ b/results/EVIDENCIAS/10 Revisión final/CHECKLIST_COMPLETADO_2026-09-13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/56df2b9a7ccb28b8/Desktop/ARTICULO DE PSILOCIBINA/gitubn/Rama-de-revisi-n-sistem-tica-/results/EVIDENCIAS/10 Revisión final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="198" documentId="8_{E1C8554C-025E-4E4E-8C6E-5DB9F1AEFEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EDD53AF-B479-4621-B4CD-812FA7778DB8}"/>
+  <xr:revisionPtr revIDLastSave="216" documentId="8_{E1C8554C-025E-4E4E-8C6E-5DB9F1AEFEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3576A801-13EE-43E4-AFD6-BEDB554AACB8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{410CF46D-D88C-4FDB-B3F4-1A2302ECC639}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="468">
   <si>
     <t>RESUMEN</t>
   </si>
@@ -1491,6 +1491,9 @@
   </si>
   <si>
     <t>Cribado pendiente de completar en Rayyan</t>
+  </si>
+  <si>
+    <t>|</t>
   </si>
 </sst>
 </file>
@@ -4513,7 +4516,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1513EB65-BE9C-4511-8418-923D282C0CFC}" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1513EB65-BE9C-4511-8418-923D282C0CFC}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
@@ -4975,9 +4978,9 @@
     <col min="4" max="4" width="10.42578125" style="35" customWidth="1"/>
     <col min="5" max="5" width="48.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="12" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
     <col min="10" max="14" width="8" customWidth="1"/>
     <col min="15" max="15" width="12.28515625" customWidth="1"/>
     <col min="16" max="16" width="24.5703125" customWidth="1"/>
@@ -5362,7 +5365,7 @@
       </c>
       <c r="J41" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D41,1),Checklist!$E:$E,TRUE),G41)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D41,1),Checklist!$F:$F,TRUE),G41)</f>
@@ -5396,7 +5399,7 @@
       </c>
       <c r="F42" s="52">
         <f t="shared" si="0"/>
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="G42">
         <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D42,1))</f>
@@ -5404,15 +5407,15 @@
       </c>
       <c r="H42">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I42">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D42,1),Checklist!$J:$J,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J42" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D42,1),Checklist!$E:$E,TRUE),G42)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K42" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D42,1),Checklist!$F:$F,TRUE),G42)</f>
@@ -5497,9 +5500,8 @@
       <c r="E44" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F44" s="52">
-        <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
+      <c r="F44" s="52" t="s">
+        <v>467</v>
       </c>
       <c r="G44">
         <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D44,1))</f>
@@ -5593,7 +5595,7 @@
     <row r="46" spans="2:18" ht="26.25" customHeight="1">
       <c r="F46" s="52">
         <f t="shared" si="0"/>
-        <v>0.83458646616541354</v>
+        <v>0.82706766917293228</v>
       </c>
       <c r="G46">
         <f>SUM(G36:G45)</f>
@@ -5601,11 +5603,11 @@
       </c>
       <c r="H46">
         <f t="shared" ref="H46:I46" si="2">SUM(H36:H45)</f>
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I46">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J46" s="37" t="e">
         <f>_xlfn.PERCENTOF(J36:J45,$G46)</f>
@@ -5941,6 +5943,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7648BC2A-312E-453A-BBA9-B96484F08716}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P190"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
@@ -5992,7 +5995,7 @@
       <c r="L1" s="41"/>
       <c r="P1" s="53"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" hidden="1">
       <c r="A2" s="60"/>
       <c r="C2" s="21" t="s">
         <v>32</v>
@@ -6009,7 +6012,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" hidden="1">
       <c r="A3" t="s">
         <v>368</v>
       </c>
@@ -6044,7 +6047,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" hidden="1">
       <c r="A4" s="60"/>
       <c r="C4" s="21" t="s">
         <v>0</v>
@@ -6097,7 +6100,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" hidden="1">
       <c r="A6" s="60"/>
       <c r="C6" s="21" t="s">
         <v>37</v>
@@ -6185,7 +6188,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" hidden="1">
       <c r="A9" s="60"/>
       <c r="C9" s="21" t="s">
         <v>42</v>
@@ -6203,7 +6206,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="25.5">
+    <row r="10" spans="1:16" ht="25.5" hidden="1">
       <c r="A10" t="s">
         <v>369</v>
       </c>
@@ -6238,7 +6241,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="38.25">
+    <row r="11" spans="1:16" ht="38.25" hidden="1">
       <c r="A11" t="s">
         <v>370</v>
       </c>
@@ -6273,7 +6276,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="25.5">
+    <row r="12" spans="1:16" ht="25.5" hidden="1">
       <c r="A12" t="s">
         <v>369</v>
       </c>
@@ -6308,7 +6311,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="63.75">
+    <row r="13" spans="1:16" ht="63.75" hidden="1">
       <c r="A13" t="s">
         <v>371</v>
       </c>
@@ -6343,7 +6346,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="18" customHeight="1">
+    <row r="14" spans="1:16" ht="18" hidden="1" customHeight="1">
       <c r="A14" t="s">
         <v>372</v>
       </c>
@@ -6357,7 +6360,7 @@
         <v>52</v>
       </c>
       <c r="E14" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="3" t="b">
         <v>0</v>
@@ -6378,7 +6381,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="18" customHeight="1">
+    <row r="15" spans="1:16" ht="18" hidden="1" customHeight="1">
       <c r="A15" t="s">
         <v>372</v>
       </c>
@@ -6392,7 +6395,7 @@
         <v>55</v>
       </c>
       <c r="E15" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="3" t="b">
         <v>0</v>
@@ -6413,7 +6416,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="38.25" customHeight="1">
+    <row r="16" spans="1:16" ht="38.25" hidden="1" customHeight="1">
       <c r="A16" t="s">
         <v>374</v>
       </c>
@@ -6446,7 +6449,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="51">
+    <row r="17" spans="1:11" ht="51" hidden="1">
       <c r="A17" t="s">
         <v>373</v>
       </c>
@@ -6460,7 +6463,7 @@
         <v>59</v>
       </c>
       <c r="E17" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="3" t="b">
         <v>0</v>
@@ -6481,7 +6484,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="38.25">
+    <row r="18" spans="1:11" ht="38.25" hidden="1">
       <c r="A18" t="s">
         <v>373</v>
       </c>
@@ -6495,7 +6498,7 @@
         <v>61</v>
       </c>
       <c r="E18" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="3" t="b">
         <v>0</v>
@@ -6516,7 +6519,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="38.25">
+    <row r="19" spans="1:11" ht="38.25" hidden="1">
       <c r="A19" t="s">
         <v>374</v>
       </c>
@@ -6551,7 +6554,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="38.25" customHeight="1">
+    <row r="20" spans="1:11" ht="38.25" hidden="1" customHeight="1">
       <c r="A20" t="s">
         <v>374</v>
       </c>
@@ -6586,7 +6589,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="25.5" customHeight="1">
+    <row r="21" spans="1:11" ht="25.5" hidden="1" customHeight="1">
       <c r="A21" t="s">
         <v>374</v>
       </c>
@@ -6621,7 +6624,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="51" customHeight="1">
+    <row r="22" spans="1:11" ht="51" hidden="1" customHeight="1">
       <c r="A22" t="s">
         <v>374</v>
       </c>
@@ -6654,7 +6657,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="25.5" customHeight="1">
+    <row r="23" spans="1:11" ht="25.5" hidden="1" customHeight="1">
       <c r="A23" t="s">
         <v>374</v>
       </c>
@@ -6687,7 +6690,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="25.5" customHeight="1">
+    <row r="24" spans="1:11" ht="25.5" hidden="1" customHeight="1">
       <c r="A24" t="s">
         <v>374</v>
       </c>
@@ -6722,7 +6725,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="38.25">
+    <row r="25" spans="1:11" ht="38.25" hidden="1">
       <c r="A25" t="s">
         <v>373</v>
       </c>
@@ -6757,7 +6760,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="25.5">
+    <row r="26" spans="1:11" ht="25.5" hidden="1">
       <c r="A26" t="s">
         <v>373</v>
       </c>
@@ -6786,13 +6789,13 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" hidden="1">
       <c r="A27" s="60"/>
       <c r="C27" s="21" t="s">
         <v>1</v>
@@ -6810,7 +6813,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="38.25">
+    <row r="28" spans="1:11" ht="38.25" hidden="1">
       <c r="A28" t="s">
         <v>374</v>
       </c>
@@ -6845,7 +6848,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="25.5" customHeight="1">
+    <row r="29" spans="1:11" ht="25.5" hidden="1" customHeight="1">
       <c r="A29" t="s">
         <v>374</v>
       </c>
@@ -6880,7 +6883,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="25.5">
+    <row r="30" spans="1:11" ht="25.5" hidden="1">
       <c r="A30" t="s">
         <v>374</v>
       </c>
@@ -6915,7 +6918,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="38.25">
+    <row r="31" spans="1:11" ht="38.25" hidden="1">
       <c r="A31" t="s">
         <v>373</v>
       </c>
@@ -6950,7 +6953,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="51">
+    <row r="32" spans="1:11" ht="51" hidden="1">
       <c r="A32" t="s">
         <v>374</v>
       </c>
@@ -6985,7 +6988,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="25.5">
+    <row r="33" spans="1:11" ht="25.5" hidden="1">
       <c r="A33" t="s">
         <v>374</v>
       </c>
@@ -7020,7 +7023,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="51" customHeight="1">
+    <row r="34" spans="1:11" ht="51" hidden="1" customHeight="1">
       <c r="A34" t="s">
         <v>374</v>
       </c>
@@ -7053,7 +7056,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="25.5" customHeight="1">
+    <row r="35" spans="1:11" ht="25.5" hidden="1" customHeight="1">
       <c r="A35" t="s">
         <v>374</v>
       </c>
@@ -7088,7 +7091,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="25.5" customHeight="1">
+    <row r="36" spans="1:11" ht="25.5" hidden="1" customHeight="1">
       <c r="A36" t="s">
         <v>374</v>
       </c>
@@ -7123,7 +7126,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="25.5">
+    <row r="37" spans="1:11" ht="25.5" hidden="1">
       <c r="A37" t="s">
         <v>373</v>
       </c>
@@ -7158,7 +7161,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="25.5">
+    <row r="38" spans="1:11" ht="25.5" hidden="1">
       <c r="A38" t="s">
         <v>373</v>
       </c>
@@ -7193,7 +7196,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" hidden="1">
       <c r="A39" s="60"/>
       <c r="C39" s="21" t="s">
         <v>105</v>
@@ -7345,7 +7348,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" hidden="1">
       <c r="A44" s="60"/>
       <c r="C44" s="21" t="s">
         <v>115</v>
@@ -7363,7 +7366,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="25.5">
+    <row r="45" spans="1:11" ht="25.5" hidden="1">
       <c r="A45" t="s">
         <v>368</v>
       </c>
@@ -7398,7 +7401,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="25.5">
+    <row r="46" spans="1:11" ht="25.5" hidden="1">
       <c r="A46" t="s">
         <v>368</v>
       </c>
@@ -7433,7 +7436,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="25.5" customHeight="1">
+    <row r="47" spans="1:11" ht="25.5" hidden="1" customHeight="1">
       <c r="A47" t="s">
         <v>368</v>
       </c>
@@ -7466,7 +7469,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="25.5">
+    <row r="48" spans="1:11" ht="25.5" hidden="1">
       <c r="A48" t="s">
         <v>368</v>
       </c>
@@ -7536,7 +7539,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="51">
+    <row r="50" spans="1:11" ht="51" hidden="1">
       <c r="A50" t="s">
         <v>376</v>
       </c>
@@ -7571,7 +7574,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" hidden="1">
       <c r="A51" s="60"/>
       <c r="C51" s="22" t="s">
         <v>135</v>
@@ -7588,7 +7591,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" hidden="1">
       <c r="A52" t="s">
         <v>376</v>
       </c>
@@ -7621,7 +7624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" hidden="1">
       <c r="A53" s="60"/>
       <c r="C53" s="22" t="s">
         <v>137</v>
@@ -7672,7 +7675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" hidden="1">
       <c r="A55" s="60"/>
       <c r="C55" s="22" t="s">
         <v>139</v>
@@ -7723,7 +7726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="38.25">
+    <row r="57" spans="1:11" ht="38.25" hidden="1">
       <c r="A57" t="s">
         <v>370</v>
       </c>
@@ -7756,7 +7759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="25.5">
+    <row r="58" spans="1:11" ht="25.5" hidden="1">
       <c r="A58" t="s">
         <v>373</v>
       </c>
@@ -7789,7 +7792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="25.5">
+    <row r="59" spans="1:11" ht="25.5" hidden="1">
       <c r="A59" t="s">
         <v>374</v>
       </c>
@@ -7822,7 +7825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" hidden="1">
       <c r="A60" s="60"/>
       <c r="C60" s="22" t="s">
         <v>148</v>
@@ -7837,7 +7840,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="25.5">
+    <row r="61" spans="1:11" ht="25.5" hidden="1">
       <c r="A61" t="s">
         <v>374</v>
       </c>
@@ -7870,7 +7873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="63.75">
+    <row r="62" spans="1:11" ht="63.75" hidden="1">
       <c r="A62" t="s">
         <v>374</v>
       </c>
@@ -7903,7 +7906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" hidden="1">
       <c r="A63" s="60"/>
       <c r="C63" s="22" t="s">
         <v>153</v>
@@ -7918,7 +7921,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="25.5">
+    <row r="64" spans="1:11" ht="25.5" hidden="1">
       <c r="A64" t="s">
         <v>375</v>
       </c>
@@ -7951,7 +7954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="25.5">
+    <row r="65" spans="1:11" ht="25.5" hidden="1">
       <c r="A65" t="s">
         <v>375</v>
       </c>
@@ -7984,7 +7987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="30">
+    <row r="66" spans="1:11" ht="30" hidden="1">
       <c r="A66" s="60"/>
       <c r="C66" s="23" t="s">
         <v>158</v>
@@ -8001,7 +8004,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="30">
+    <row r="67" spans="1:11" ht="30" hidden="1">
       <c r="A67" t="s">
         <v>369</v>
       </c>
@@ -8034,7 +8037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="45">
+    <row r="68" spans="1:11" ht="45" hidden="1">
       <c r="A68" t="s">
         <v>369</v>
       </c>
@@ -8067,7 +8070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="30">
+    <row r="69" spans="1:11" ht="30" hidden="1">
       <c r="A69" t="s">
         <v>369</v>
       </c>
@@ -8103,7 +8106,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="45">
+    <row r="70" spans="1:11" ht="45" hidden="1">
       <c r="A70" t="s">
         <v>369</v>
       </c>
@@ -8139,7 +8142,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="75">
+    <row r="71" spans="1:11" ht="75" hidden="1">
       <c r="A71" t="s">
         <v>369</v>
       </c>
@@ -8175,7 +8178,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="30">
+    <row r="72" spans="1:11" ht="30" hidden="1">
       <c r="A72" t="s">
         <v>369</v>
       </c>
@@ -8211,7 +8214,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="30">
+    <row r="73" spans="1:11" ht="30" hidden="1">
       <c r="A73" t="s">
         <v>369</v>
       </c>
@@ -8247,7 +8250,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" hidden="1">
       <c r="A74" t="s">
         <v>369</v>
       </c>
@@ -8264,7 +8267,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="45">
+    <row r="75" spans="1:11" ht="45" hidden="1">
       <c r="A75" t="s">
         <v>369</v>
       </c>
@@ -8297,7 +8300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="45">
+    <row r="76" spans="1:11" ht="45" hidden="1">
       <c r="A76" t="s">
         <v>369</v>
       </c>
@@ -8330,7 +8333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="45">
+    <row r="77" spans="1:11" ht="45" hidden="1">
       <c r="A77" t="s">
         <v>369</v>
       </c>
@@ -8366,7 +8369,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="45">
+    <row r="78" spans="1:11" ht="45" hidden="1">
       <c r="A78" t="s">
         <v>369</v>
       </c>
@@ -8399,7 +8402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="30">
+    <row r="79" spans="1:11" ht="30" hidden="1">
       <c r="A79" t="s">
         <v>369</v>
       </c>
@@ -8435,7 +8438,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="30">
+    <row r="80" spans="1:11" ht="30" hidden="1">
       <c r="A80" t="s">
         <v>369</v>
       </c>
@@ -8471,7 +8474,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" hidden="1">
       <c r="A81" s="60"/>
       <c r="C81" s="23" t="s">
         <v>186</v>
@@ -8486,7 +8489,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="30">
+    <row r="82" spans="1:11" ht="30" hidden="1">
       <c r="A82" t="s">
         <v>369</v>
       </c>
@@ -8522,7 +8525,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" hidden="1">
       <c r="A83" s="60"/>
       <c r="C83" s="23" t="s">
         <v>189</v>
@@ -8537,7 +8540,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="30">
+    <row r="84" spans="1:11" ht="30" hidden="1">
       <c r="A84" t="s">
         <v>369</v>
       </c>
@@ -8573,7 +8576,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="30">
+    <row r="85" spans="1:11" ht="30" hidden="1">
       <c r="A85" t="s">
         <v>369</v>
       </c>
@@ -8609,7 +8612,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="30">
+    <row r="86" spans="1:11" ht="30" hidden="1">
       <c r="A86" s="60"/>
       <c r="C86" s="24" t="s">
         <v>278</v>
@@ -8626,7 +8629,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="15" customHeight="1">
+    <row r="87" spans="1:11" ht="15" hidden="1" customHeight="1">
       <c r="A87" t="s">
         <v>369</v>
       </c>
@@ -8659,7 +8662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" hidden="1">
       <c r="A88" t="s">
         <v>369</v>
       </c>
@@ -8688,7 +8691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" hidden="1">
       <c r="A89" t="s">
         <v>369</v>
       </c>
@@ -8717,7 +8720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" hidden="1">
       <c r="A90" t="s">
         <v>369</v>
       </c>
@@ -8746,7 +8749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="30">
+    <row r="91" spans="1:11" ht="30" hidden="1">
       <c r="A91" t="s">
         <v>369</v>
       </c>
@@ -8775,7 +8778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" hidden="1">
       <c r="A92" t="s">
         <v>369</v>
       </c>
@@ -8807,7 +8810,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="15" customHeight="1">
+    <row r="93" spans="1:11" ht="15" hidden="1" customHeight="1">
       <c r="A93" t="s">
         <v>369</v>
       </c>
@@ -8840,7 +8843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="30">
+    <row r="94" spans="1:11" ht="30" hidden="1">
       <c r="A94" t="s">
         <v>369</v>
       </c>
@@ -8869,7 +8872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="30">
+    <row r="95" spans="1:11" ht="30" hidden="1">
       <c r="A95" t="s">
         <v>369</v>
       </c>
@@ -8901,7 +8904,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="30">
+    <row r="96" spans="1:11" ht="30" hidden="1">
       <c r="A96" t="s">
         <v>369</v>
       </c>
@@ -8933,7 +8936,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="30">
+    <row r="97" spans="1:11" ht="30" hidden="1">
       <c r="A97" t="s">
         <v>369</v>
       </c>
@@ -8965,7 +8968,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="15" customHeight="1">
+    <row r="98" spans="1:11" ht="15" hidden="1" customHeight="1">
       <c r="A98" t="s">
         <v>369</v>
       </c>
@@ -8998,7 +9001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="30">
+    <row r="99" spans="1:11" ht="30" hidden="1">
       <c r="A99" t="s">
         <v>369</v>
       </c>
@@ -9027,7 +9030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" hidden="1">
       <c r="A100" t="s">
         <v>369</v>
       </c>
@@ -9059,7 +9062,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" hidden="1">
       <c r="A101" t="s">
         <v>369</v>
       </c>
@@ -9088,7 +9091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="30">
+    <row r="102" spans="1:11" ht="30" hidden="1">
       <c r="A102" t="s">
         <v>369</v>
       </c>
@@ -9120,7 +9123,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" hidden="1">
       <c r="A103" t="s">
         <v>369</v>
       </c>
@@ -9149,7 +9152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="30">
+    <row r="104" spans="1:11" ht="30" hidden="1">
       <c r="A104" t="s">
         <v>369</v>
       </c>
@@ -9181,7 +9184,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" hidden="1">
       <c r="A105" t="s">
         <v>369</v>
       </c>
@@ -9213,7 +9216,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="30">
+    <row r="106" spans="1:11" ht="30" hidden="1">
       <c r="A106" t="s">
         <v>369</v>
       </c>
@@ -9242,7 +9245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="30" customHeight="1">
+    <row r="107" spans="1:11" ht="30" hidden="1" customHeight="1">
       <c r="A107" t="s">
         <v>369</v>
       </c>
@@ -9278,7 +9281,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="30">
+    <row r="108" spans="1:11" ht="30" hidden="1">
       <c r="A108" t="s">
         <v>369</v>
       </c>
@@ -9310,7 +9313,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="30">
+    <row r="109" spans="1:11" ht="30" hidden="1">
       <c r="A109" t="s">
         <v>369</v>
       </c>
@@ -9342,7 +9345,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" hidden="1">
       <c r="A110" t="s">
         <v>369</v>
       </c>
@@ -9371,7 +9374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="30">
+    <row r="111" spans="1:11" ht="30" hidden="1">
       <c r="A111" t="s">
         <v>369</v>
       </c>
@@ -9400,7 +9403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="45">
+    <row r="112" spans="1:11" ht="45" hidden="1">
       <c r="A112" t="s">
         <v>369</v>
       </c>
@@ -9432,7 +9435,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="60">
+    <row r="113" spans="1:11" ht="60" hidden="1">
       <c r="A113" t="s">
         <v>369</v>
       </c>
@@ -9461,7 +9464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="30">
+    <row r="114" spans="1:11" ht="30" hidden="1">
       <c r="A114" t="s">
         <v>369</v>
       </c>
@@ -9493,7 +9496,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="15" customHeight="1">
+    <row r="115" spans="1:11" ht="15" hidden="1" customHeight="1">
       <c r="A115" t="s">
         <v>369</v>
       </c>
@@ -9526,7 +9529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="30">
+    <row r="116" spans="1:11" ht="30" hidden="1">
       <c r="A116" t="s">
         <v>369</v>
       </c>
@@ -9555,7 +9558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="45">
+    <row r="117" spans="1:11" ht="45" hidden="1">
       <c r="A117" t="s">
         <v>369</v>
       </c>
@@ -9587,7 +9590,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="30">
+    <row r="118" spans="1:11" ht="30" hidden="1">
       <c r="A118" t="s">
         <v>369</v>
       </c>
@@ -9620,7 +9623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="30">
+    <row r="119" spans="1:11" ht="30" hidden="1">
       <c r="A119" t="s">
         <v>369</v>
       </c>
@@ -9649,7 +9652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="45">
+    <row r="120" spans="1:11" ht="45" hidden="1">
       <c r="A120" t="s">
         <v>369</v>
       </c>
@@ -9678,7 +9681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" hidden="1">
       <c r="A121" t="s">
         <v>369</v>
       </c>
@@ -9710,7 +9713,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="15" customHeight="1">
+    <row r="122" spans="1:11" ht="15" hidden="1" customHeight="1">
       <c r="A122" s="60"/>
       <c r="B122" s="30" t="s">
         <v>279</v>
@@ -9728,7 +9731,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="12.75" customHeight="1">
+    <row r="123" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A123" s="35" t="s">
         <v>367</v>
       </c>
@@ -9758,7 +9761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="12.75" customHeight="1">
+    <row r="124" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A124" s="35" t="s">
         <v>367</v>
       </c>
@@ -9791,7 +9794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="12.75" customHeight="1">
+    <row r="125" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A125" s="35" t="s">
         <v>367</v>
       </c>
@@ -9827,7 +9830,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="12.75" customHeight="1">
+    <row r="126" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A126" s="35" t="s">
         <v>367</v>
       </c>
@@ -9863,7 +9866,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="12.75" customHeight="1">
+    <row r="127" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A127" s="35" t="s">
         <v>367</v>
       </c>
@@ -9880,7 +9883,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="12.75" customHeight="1">
+    <row r="128" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A128" s="35" t="s">
         <v>367</v>
       </c>
@@ -9916,7 +9919,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="12.75" customHeight="1">
+    <row r="129" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A129" s="35" t="s">
         <v>367</v>
       </c>
@@ -9952,7 +9955,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="12.75" customHeight="1">
+    <row r="130" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A130" s="35" t="s">
         <v>367</v>
       </c>
@@ -9988,7 +9991,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="12.75" customHeight="1">
+    <row r="131" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A131" s="35" t="s">
         <v>367</v>
       </c>
@@ -10005,7 +10008,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="12.75" customHeight="1">
+    <row r="132" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A132" s="35" t="s">
         <v>367</v>
       </c>
@@ -10041,7 +10044,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="12.75" customHeight="1">
+    <row r="133" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A133" s="35" t="s">
         <v>367</v>
       </c>
@@ -10077,7 +10080,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="12.75" customHeight="1">
+    <row r="134" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A134" s="35" t="s">
         <v>367</v>
       </c>
@@ -10113,7 +10116,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="12.75" customHeight="1">
+    <row r="135" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A135" s="35" t="s">
         <v>367</v>
       </c>
@@ -10130,7 +10133,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="12.75" customHeight="1">
+    <row r="136" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A136" s="35" t="s">
         <v>367</v>
       </c>
@@ -10163,7 +10166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="12.75" customHeight="1">
+    <row r="137" spans="1:11" ht="12.75" hidden="1" customHeight="1">
       <c r="A137" s="35" t="s">
         <v>367</v>
       </c>
@@ -10196,7 +10199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" hidden="1">
       <c r="A138" s="60"/>
       <c r="C138" s="51" t="s">
         <v>10</v>
@@ -10211,7 +10214,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="57">
+    <row r="139" spans="1:11" ht="57" hidden="1">
       <c r="A139" t="s">
         <v>368</v>
       </c>
@@ -10244,7 +10247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="42.75">
+    <row r="140" spans="1:11" ht="42.75" hidden="1">
       <c r="A140" t="s">
         <v>368</v>
       </c>
@@ -10277,7 +10280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="42.75">
+    <row r="141" spans="1:11" ht="42.75" hidden="1">
       <c r="A141" t="s">
         <v>368</v>
       </c>
@@ -10310,7 +10313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="15" customHeight="1">
+    <row r="142" spans="1:11" ht="15" hidden="1" customHeight="1">
       <c r="A142" s="60"/>
       <c r="C142" s="51" t="s">
         <v>163</v>
@@ -10325,7 +10328,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="28.5">
+    <row r="143" spans="1:11" ht="28.5" hidden="1">
       <c r="A143" t="s">
         <v>368</v>
       </c>
@@ -10358,7 +10361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="42.75">
+    <row r="144" spans="1:11" ht="42.75" hidden="1">
       <c r="A144" t="s">
         <v>368</v>
       </c>
@@ -10391,7 +10394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="42.75">
+    <row r="145" spans="1:11" ht="42.75" hidden="1">
       <c r="A145" t="s">
         <v>368</v>
       </c>
@@ -10424,7 +10427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="42.75">
+    <row r="146" spans="1:11" ht="42.75" hidden="1">
       <c r="A146" t="s">
         <v>368</v>
       </c>
@@ -10457,7 +10460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="42.75">
+    <row r="147" spans="1:11" ht="42.75" hidden="1">
       <c r="A147" t="s">
         <v>368</v>
       </c>
@@ -10493,7 +10496,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="57">
+    <row r="148" spans="1:11" ht="57" hidden="1">
       <c r="A148" t="s">
         <v>368</v>
       </c>
@@ -10526,7 +10529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" hidden="1">
       <c r="A149" s="60"/>
       <c r="C149" s="51" t="s">
         <v>332</v>
@@ -10541,7 +10544,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="28.5">
+    <row r="150" spans="1:11" ht="28.5" hidden="1">
       <c r="A150" t="s">
         <v>368</v>
       </c>
@@ -10574,7 +10577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="57">
+    <row r="151" spans="1:11" ht="57" hidden="1">
       <c r="A151" t="s">
         <v>368</v>
       </c>
@@ -10605,7 +10608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="28.5">
+    <row r="152" spans="1:11" ht="28.5" hidden="1">
       <c r="A152" t="s">
         <v>368</v>
       </c>
@@ -10639,7 +10642,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="28.5">
+    <row r="153" spans="1:11" ht="28.5" hidden="1">
       <c r="A153" t="s">
         <v>368</v>
       </c>
@@ -10673,7 +10676,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="28.5">
+    <row r="154" spans="1:11" ht="28.5" hidden="1">
       <c r="A154" t="s">
         <v>368</v>
       </c>
@@ -10706,7 +10709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="43.5" thickBot="1">
+    <row r="155" spans="1:11" ht="43.5" hidden="1" thickBot="1">
       <c r="A155" t="s">
         <v>368</v>
       </c>
@@ -10777,7 +10780,18 @@
     <row r="189" ht="18" customHeight="1"/>
     <row r="190" ht="18" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:K155" xr:uid="{7648BC2A-312E-453A-BBA9-B96484F08716}"/>
+  <autoFilter ref="A1:K155" xr:uid="{7648BC2A-312E-453A-BBA9-B96484F08716}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="9 Redacción"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="10">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="J3 J5 J7:J8 J10:J26 J28:J38 J40:J43 J45:J50 J52 J54 J56:J59 J61:J62 J64:J65 J67:J80 J82 J84:J85 J87:J126 J128:J130 J132:J134 J136:J155">
     <cfRule type="cellIs" dxfId="6" priority="2" operator="between">
       <formula>1</formula>

--- a/results/EVIDENCIAS/10 Revisión final/CHECKLIST_COMPLETADO_2026-09-13.xlsx
+++ b/results/EVIDENCIAS/10 Revisión final/CHECKLIST_COMPLETADO_2026-09-13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/56df2b9a7ccb28b8/Desktop/ARTICULO DE PSILOCIBINA/gitubn/Rama-de-revisi-n-sistem-tica-/results/EVIDENCIAS/10 Revisión final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="216" documentId="8_{E1C8554C-025E-4E4E-8C6E-5DB9F1AEFEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3576A801-13EE-43E4-AFD6-BEDB554AACB8}"/>
+  <xr:revisionPtr revIDLastSave="248" documentId="8_{E1C8554C-025E-4E4E-8C6E-5DB9F1AEFEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{265BE39D-E735-40F3-A0BA-2AFC5B337907}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{410CF46D-D88C-4FDB-B3F4-1A2302ECC639}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="3" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="425">
   <si>
     <t>RESUMEN</t>
   </si>
@@ -1253,7 +1253,7 @@
     <t>BASES DE DATOS EN PROTOVOLO</t>
   </si>
   <si>
-    <t>;C]</t>
+    <t>registradp</t>
   </si>
   <si>
     <t>ACTUALIZAR JUSTI</t>
@@ -1364,136 +1364,7 @@
     <t>.</t>
   </si>
   <si>
-    <t>Evaluación basada en manuscrito; fase pendiente o parcial.</t>
-  </si>
-  <si>
-    <t>Código y corpus disponibles; formularios y datos clínicos finales pendientes.</t>
-  </si>
-  <si>
-    <t>Corpus, tablas, estrategias, pipeline y repositorio disponibles; datos clínicos pendientes.</t>
-  </si>
-  <si>
-    <t>Contribuciones CRediT pendientes.</t>
-  </si>
-  <si>
-    <t>Ausencia de financiamiento externo y conflicto de intereses declarada.</t>
-  </si>
-  <si>
-    <t>Registro PROSPERO CRD420261493650 y versión 1.2 informados.</t>
-  </si>
-  <si>
-    <t>Implicaciones futuras señaladas; no hay implicaciones clínicas finales.</t>
-  </si>
-  <si>
-    <t>Limitaciones del flujo PRISMA y ausencia de extracción clínica reconocidas.</t>
-  </si>
-  <si>
-    <t>Limitaciones de placebo, desenmascaramiento, apoyo y seguimiento discutidas.</t>
-  </si>
-  <si>
-    <t>Discusión provisional; falta discusión de evidencia clínica incluida.</t>
-  </si>
-  <si>
-    <t>No se ha aplicado GRADE a resultados clínicos.</t>
-  </si>
-  <si>
-    <t>No se ha evaluado sesgo de notificación en síntesis.</t>
-  </si>
-  <si>
-    <t>No se han realizado análisis de sensibilidad.</t>
-  </si>
-  <si>
-    <t>No se han explorado causas de heterogeneidad.</t>
-  </si>
-  <si>
-    <t>No hay metaanálisis ni estimaciones agrupadas.</t>
-  </si>
-  <si>
-    <t>No se ha realizado síntesis de estudios incluidos.</t>
-  </si>
-  <si>
-    <t>No hay resultados individuales ni estimaciones de efecto.</t>
-  </si>
-  <si>
-    <t>No hay evaluación de riesgo de sesgo por estudio.</t>
-  </si>
-  <si>
-    <t>No hay tabla de características de estudios incluidos.</t>
-  </si>
-  <si>
-    <t>No se han documentado estudios excluidos con motivos.</t>
-  </si>
-  <si>
-    <t>943 registros, 417 duplicados, 1 retractado y 525 para cribado; etapas posteriores NR.</t>
-  </si>
-  <si>
-    <t>GRADE previsto; aún no aplicado.</t>
-  </si>
-  <si>
-    <t>No se ha evaluado sesgo de notificación.</t>
-  </si>
-  <si>
-    <t>No se han realizado análisis de heterogeneidad.</t>
-  </si>
-  <si>
-    <t>Metaanálisis condicionado a homogeneidad; no ejecutado.</t>
-  </si>
-  <si>
-    <t>Se prevén tablas y síntesis narrativa; tablas finales pendientes.</t>
-  </si>
-  <si>
-    <t>Manejo general descrito; faltan conversiones y datos faltantes.</t>
-  </si>
-  <si>
-    <t>Agrupación prevista por diagnóstico, comparador, dosis, apoyo y seguimiento.</t>
-  </si>
-  <si>
-    <t>Se especifican DM, DME, RR e IC del 95%.</t>
-  </si>
-  <si>
-    <t>Dominios de riesgo descritos; herramienta y evaluaciones pendientes.</t>
-  </si>
-  <si>
-    <t>Variables enumeradas; datos aún no extraídos.</t>
-  </si>
-  <si>
-    <t>Desenlaces clínicos y de seguridad enumerados.</t>
-  </si>
-  <si>
-    <t>Extracción descrita como plan; tabla clínica aún no completada.</t>
-  </si>
-  <si>
-    <t>Dos revisores y consenso planificados; matriz Rayyan pendiente.</t>
-  </si>
-  <si>
-    <t>Estrategias documentadas; falta resolver inconsistencias de fuente y resultados.</t>
-  </si>
-  <si>
-    <t>Fuentes y fecha documentadas; falta armonizar Scopus/Ovid y conteos.</t>
-  </si>
-  <si>
-    <t>PICOS y exclusiones definidos para adultos de 18–65 años.</t>
-  </si>
-  <si>
-    <t>Objetivos general y específicos declarados.</t>
-  </si>
-  <si>
-    <t>Introducción justifica la revisión y separa evidencia bibliométrica y clínica.</t>
-  </si>
-  <si>
-    <t>Resumen estructurado incompleto; la sección Resumen está vacía.</t>
-  </si>
-  <si>
-    <t>Título identifica revisión sistemática en fase de protocolo; no es artículo final.</t>
-  </si>
-  <si>
-    <t>13/09/2026</t>
-  </si>
-  <si>
-    <t>Cribado pendiente de completar en Rayyan</t>
-  </si>
-  <si>
-    <t>|</t>
+    <t>Describe roles of funder(s), sponsor(s), and/or institution(s), if any, in developing the protocol</t>
   </si>
 </sst>
 </file>
@@ -1755,7 +1626,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1980,6 +1851,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2325,9 +2202,6 @@
     <xf numFmtId="0" fontId="29" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2350,6 +2224,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2580,10 +2457,6 @@
 </FeaturePropertyBags>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Estefania Aranda Rosas" refreshedDate="46269.852720023147" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="154" xr:uid="{60FB3188-6981-4A09-95E6-C3397F2DC995}">
   <cacheSource type="worksheet">
@@ -4516,7 +4389,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1513EB65-BE9C-4511-8418-923D282C0CFC}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1513EB65-BE9C-4511-8418-923D282C0CFC}" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
@@ -4978,9 +4851,9 @@
     <col min="4" max="4" width="10.42578125" style="35" customWidth="1"/>
     <col min="5" max="5" width="48.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="8" customWidth="1"/>
     <col min="15" max="15" width="12.28515625" customWidth="1"/>
     <col min="16" max="16" width="24.5703125" customWidth="1"/>
@@ -5020,7 +4893,7 @@
     <row r="31" spans="5:6" ht="16.5" customHeight="1"/>
     <row r="32" spans="5:6" ht="16.5" customHeight="1">
       <c r="E32" s="12"/>
-      <c r="F32" s="59"/>
+      <c r="F32" s="58"/>
     </row>
     <row r="33" spans="2:18" ht="16.5" customHeight="1">
       <c r="B33" t="s">
@@ -5078,7 +4951,7 @@
       <c r="R35" s="11"/>
     </row>
     <row r="36" spans="2:18" ht="26.25" customHeight="1">
-      <c r="C36" s="63">
+      <c r="C36" s="62">
         <v>46204</v>
       </c>
       <c r="D36" s="35" t="s">
@@ -5089,7 +4962,7 @@
       </c>
       <c r="F36" s="52">
         <f t="shared" ref="F36:F46" si="0">_xlfn.PERCENTOF(H36,G36)</f>
-        <v>1</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="G36">
         <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D36,1))</f>
@@ -5097,23 +4970,23 @@
       </c>
       <c r="H36">
         <f>G36-I36</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I36">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D36,1),Checklist!$J:$J,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D36,1),Checklist!$E:$E,TRUE),G36)</f>
-        <v>0.6</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="K36" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D36,1),Checklist!$F:$F,TRUE),G36)</f>
-        <v>0.2</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="L36" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D36,1),Checklist!$G:$G,TRUE),G36)</f>
-        <v>0.53333333333333333</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="M36" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D36,1),Checklist!$H:$H,TRUE),G36)</f>
@@ -5121,9 +4994,9 @@
       </c>
       <c r="N36" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D36,1),Checklist!$I:$I,TRUE),G36)</f>
-        <v>0.4</v>
-      </c>
-      <c r="O36" s="62" t="s">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O36" s="61" t="s">
         <v>422</v>
       </c>
       <c r="P36" t="s">
@@ -5131,7 +5004,7 @@
       </c>
     </row>
     <row r="37" spans="2:18" ht="26.25" customHeight="1">
-      <c r="C37" s="63">
+      <c r="C37" s="62">
         <v>46245</v>
       </c>
       <c r="D37" s="35" t="s">
@@ -5176,7 +5049,7 @@
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D37,1),Checklist!$I:$I,TRUE),G37)</f>
         <v>0.1</v>
       </c>
-      <c r="O37" s="62" t="s">
+      <c r="O37" s="61" t="s">
         <v>415</v>
       </c>
       <c r="P37" s="2" t="s">
@@ -5187,7 +5060,7 @@
       </c>
     </row>
     <row r="38" spans="2:18" ht="26.25" customHeight="1">
-      <c r="C38" s="63">
+      <c r="C38" s="62">
         <v>46266</v>
       </c>
       <c r="D38" s="35" t="s">
@@ -5240,7 +5113,7 @@
       </c>
     </row>
     <row r="39" spans="2:18" ht="26.25" customHeight="1">
-      <c r="C39" s="63">
+      <c r="C39" s="62">
         <v>46270</v>
       </c>
       <c r="D39" s="35" t="s">
@@ -5293,52 +5166,54 @@
       </c>
     </row>
     <row r="40" spans="2:18" ht="26.25" customHeight="1">
-      <c r="C40" s="63">
+      <c r="C40" s="62">
         <v>46280</v>
       </c>
       <c r="D40" s="35" t="s">
         <v>371</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F40" s="52" t="e">
+        <v>253</v>
+      </c>
+      <c r="F40" s="52">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D40,1))</f>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I40">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D40,1),Checklist!$J:$J,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="37" t="e">
+        <v>1</v>
+      </c>
+      <c r="J40" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D40,1),Checklist!$E:$E,TRUE),G40)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K40" s="37" t="e">
+        <v>0</v>
+      </c>
+      <c r="K40" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D40,1),Checklist!$F:$F,TRUE),G40)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L40" s="37" t="e">
+        <v>0</v>
+      </c>
+      <c r="L40" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D40,1),Checklist!$G:$G,TRUE),G40)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M40" s="37" t="e">
+        <v>0</v>
+      </c>
+      <c r="M40" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D40,1),Checklist!$H:$H,TRUE),G40)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N40" s="37" t="e">
+        <v>0</v>
+      </c>
+      <c r="N40" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D40,1),Checklist!$I:$I,TRUE),G40)</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="2:18" ht="26.25" customHeight="1">
-      <c r="C41" s="63">
+      <c r="C41" s="62">
         <v>46295</v>
       </c>
       <c r="D41" s="35" t="s">
@@ -5349,7 +5224,7 @@
       </c>
       <c r="F41" s="52">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41">
         <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D41,1))</f>
@@ -5357,15 +5232,15 @@
       </c>
       <c r="H41">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I41">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D41,1),Checklist!$J:$J,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D41,1),Checklist!$E:$E,TRUE),G41)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D41,1),Checklist!$F:$F,TRUE),G41)</f>
@@ -5388,7 +5263,7 @@
       </c>
     </row>
     <row r="42" spans="2:18" ht="26.25" customHeight="1">
-      <c r="C42" s="63">
+      <c r="C42" s="62">
         <v>46310</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -5399,7 +5274,7 @@
       </c>
       <c r="F42" s="52">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G42">
         <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D42,1))</f>
@@ -5407,15 +5282,15 @@
       </c>
       <c r="H42">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I42">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D42,1),Checklist!$J:$J,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J42" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D42,1),Checklist!$E:$E,TRUE),G42)</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="K42" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D42,1),Checklist!$F:$F,TRUE),G42)</f>
@@ -5441,7 +5316,7 @@
       </c>
     </row>
     <row r="43" spans="2:18" ht="26.25" customHeight="1">
-      <c r="C43" s="63">
+      <c r="C43" s="62">
         <v>46325</v>
       </c>
       <c r="D43" s="35" t="s">
@@ -5452,7 +5327,7 @@
       </c>
       <c r="F43" s="52">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="G43">
         <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D43,1))</f>
@@ -5460,11 +5335,11 @@
       </c>
       <c r="H43">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I43">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D43,1),Checklist!$J:$J,0)</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J43" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D43,1),Checklist!$E:$E,TRUE),G43)</f>
@@ -5491,7 +5366,7 @@
       </c>
     </row>
     <row r="44" spans="2:18" ht="26.25" customHeight="1">
-      <c r="C44" s="63">
+      <c r="C44" s="62">
         <v>46341</v>
       </c>
       <c r="D44" s="35" t="s">
@@ -5500,8 +5375,9 @@
       <c r="E44" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F44" s="52" t="s">
-        <v>467</v>
+      <c r="F44" s="52">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G44">
         <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D44,1))</f>
@@ -5509,11 +5385,11 @@
       </c>
       <c r="H44">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I44">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D44,1),Checklist!$J:$J,0)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J44" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D44,1),Checklist!$E:$E,TRUE),G44)</f>
@@ -5543,7 +5419,7 @@
       </c>
     </row>
     <row r="45" spans="2:18" ht="26.25" customHeight="1">
-      <c r="C45" s="63">
+      <c r="C45" s="62">
         <v>46356</v>
       </c>
       <c r="D45" s="35" t="s">
@@ -5554,7 +5430,7 @@
       </c>
       <c r="F45" s="52">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G45">
         <f>COUNTIF(Checklist!$A:$A,TEXT(CALENDARIO!D45,1))</f>
@@ -5562,11 +5438,11 @@
       </c>
       <c r="H45">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45">
         <f>COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D45,1),Checklist!$J:$J,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J45" s="37">
         <f>_xlfn.PERCENTOF(COUNTIFS(Checklist!$A:$A,TEXT(CALENDARIO!D45,1),Checklist!$E:$E,TRUE),G45)</f>
@@ -5595,39 +5471,39 @@
     <row r="46" spans="2:18" ht="26.25" customHeight="1">
       <c r="F46" s="52">
         <f t="shared" si="0"/>
-        <v>0.82706766917293228</v>
+        <v>0.66417910447761197</v>
       </c>
       <c r="G46">
         <f>SUM(G36:G45)</f>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H46">
         <f t="shared" ref="H46:I46" si="2">SUM(H36:H45)</f>
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="I46">
         <f t="shared" si="2"/>
-        <v>24</v>
-      </c>
-      <c r="J46" s="37" t="e">
+        <v>45</v>
+      </c>
+      <c r="J46" s="37">
         <f>_xlfn.PERCENTOF(J36:J45,$G46)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="K46" s="37" t="e">
+        <v>2.3852957435046986E-2</v>
+      </c>
+      <c r="K46" s="37">
         <f>_xlfn.PERCENTOF(K36:K45,$G46)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L46" s="37" t="e">
+        <v>9.2039800995024883E-3</v>
+      </c>
+      <c r="L46" s="37">
         <f>_xlfn.PERCENTOF(L36:L45,$G46)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="M46" s="37" t="e">
+        <v>1.0475400773908237E-2</v>
+      </c>
+      <c r="M46" s="37">
         <f>_xlfn.PERCENTOF(M36:M45,$G46)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="N46" s="37" t="e">
+        <v>0</v>
+      </c>
+      <c r="N46" s="37">
         <f>_xlfn.PERCENTOF(N36:N45,$G46)</f>
-        <v>#NUM!</v>
+        <v>3.2338308457711446E-3</v>
       </c>
     </row>
   </sheetData>
@@ -5996,7 +5872,7 @@
       <c r="P1" s="53"/>
     </row>
     <row r="2" spans="1:16" hidden="1">
-      <c r="A2" s="60"/>
+      <c r="A2" s="59"/>
       <c r="C2" s="21" t="s">
         <v>32</v>
       </c>
@@ -6041,14 +5917,12 @@
         <v>0</v>
       </c>
       <c r="J3">
+        <f>COUNTIF(E3:I3,(NOT(FALSE)))</f>
         <v>2</v>
       </c>
-      <c r="K3" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="4" spans="1:16" hidden="1">
-      <c r="A4" s="60"/>
+      <c r="A4" s="59"/>
       <c r="C4" s="21" t="s">
         <v>0</v>
       </c>
@@ -6058,14 +5932,11 @@
       <c r="G4" s="33"/>
       <c r="H4" s="33"/>
       <c r="I4" s="33"/>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="J4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" hidden="1">
       <c r="A5" t="s">
         <v>375</v>
       </c>
@@ -6094,14 +5965,12 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>463</v>
+        <f>COUNTIF(E5:I5,(NOT(FALSE)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:16" hidden="1">
-      <c r="A6" s="60"/>
+      <c r="A6" s="59"/>
       <c r="C6" s="21" t="s">
         <v>37</v>
       </c>
@@ -6111,14 +5980,11 @@
       <c r="G6" s="33"/>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="25.5">
+      <c r="J6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25.5" hidden="1">
       <c r="A7" t="s">
         <v>375</v>
       </c>
@@ -6147,13 +6013,11 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="25.5">
+        <f t="shared" ref="J7:J8" si="0">COUNTIF(E7:I7,(NOT(FALSE)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25.5" hidden="1">
       <c r="A8" t="s">
         <v>375</v>
       </c>
@@ -6182,14 +6046,12 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>2</v>
-      </c>
-      <c r="K8" t="s">
-        <v>461</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:16" hidden="1">
-      <c r="A9" s="60"/>
+      <c r="A9" s="59"/>
       <c r="C9" s="21" t="s">
         <v>42</v>
       </c>
@@ -6199,14 +6061,11 @@
       <c r="G9" s="33"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="25.5" hidden="1">
+      <c r="J9" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25.5">
       <c r="A10" t="s">
         <v>369</v>
       </c>
@@ -6235,10 +6094,8 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>2</v>
-      </c>
-      <c r="K10" t="s">
-        <v>460</v>
+        <f t="shared" ref="J10:J26" si="1">COUNTIF(E10:I10,(NOT(FALSE)))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="38.25" hidden="1">
@@ -6270,13 +6127,11 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="25.5" hidden="1">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25.5">
       <c r="A12" t="s">
         <v>369</v>
       </c>
@@ -6305,10 +6160,8 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12" t="s">
-        <v>458</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="63.75" hidden="1">
@@ -6340,10 +6193,8 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13" t="s">
-        <v>457</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" hidden="1" customHeight="1">
@@ -6360,7 +6211,7 @@
         <v>52</v>
       </c>
       <c r="E14" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="b">
         <v>0</v>
@@ -6375,10 +6226,8 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14" t="s">
-        <v>456</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="18" hidden="1" customHeight="1">
@@ -6395,7 +6244,7 @@
         <v>55</v>
       </c>
       <c r="E15" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="b">
         <v>0</v>
@@ -6410,10 +6259,8 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>2</v>
-      </c>
-      <c r="K15" t="s">
-        <v>455</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="38.25" hidden="1" customHeight="1">
@@ -6443,13 +6290,11 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="51" hidden="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="51" hidden="1">
       <c r="A17" t="s">
         <v>373</v>
       </c>
@@ -6463,7 +6308,7 @@
         <v>59</v>
       </c>
       <c r="E17" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3" t="b">
         <v>0</v>
@@ -6478,13 +6323,11 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="38.25" hidden="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="38.25" hidden="1">
       <c r="A18" t="s">
         <v>373</v>
       </c>
@@ -6498,7 +6341,7 @@
         <v>61</v>
       </c>
       <c r="E18" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3" t="b">
         <v>0</v>
@@ -6513,13 +6356,11 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>2</v>
-      </c>
-      <c r="K18" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="38.25" hidden="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="38.25" hidden="1">
       <c r="A19" t="s">
         <v>374</v>
       </c>
@@ -6548,13 +6389,11 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="38.25" hidden="1" customHeight="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="38.25" hidden="1" customHeight="1">
       <c r="A20" t="s">
         <v>374</v>
       </c>
@@ -6583,13 +6422,11 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="25.5" hidden="1" customHeight="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="25.5" hidden="1" customHeight="1">
       <c r="A21" t="s">
         <v>374</v>
       </c>
@@ -6618,13 +6455,11 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="51" hidden="1" customHeight="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="51" hidden="1" customHeight="1">
       <c r="A22" t="s">
         <v>374</v>
       </c>
@@ -6651,13 +6486,11 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="25.5" hidden="1" customHeight="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="25.5" hidden="1" customHeight="1">
       <c r="A23" t="s">
         <v>374</v>
       </c>
@@ -6684,13 +6517,11 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="25.5" hidden="1" customHeight="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="25.5" hidden="1" customHeight="1">
       <c r="A24" t="s">
         <v>374</v>
       </c>
@@ -6719,13 +6550,11 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="38.25" hidden="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="38.25" hidden="1">
       <c r="A25" t="s">
         <v>373</v>
       </c>
@@ -6754,13 +6583,11 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="25.5" hidden="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="25.5" hidden="1">
       <c r="A26" t="s">
         <v>373</v>
       </c>
@@ -6789,14 +6616,12 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" hidden="1">
-      <c r="A27" s="60"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" hidden="1">
+      <c r="A27" s="59"/>
       <c r="C27" s="21" t="s">
         <v>1</v>
       </c>
@@ -6806,14 +6631,11 @@
       <c r="G27" s="33"/>
       <c r="H27" s="33"/>
       <c r="I27" s="33"/>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="38.25" hidden="1">
+      <c r="J27" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="38.25" hidden="1">
       <c r="A28" t="s">
         <v>374</v>
       </c>
@@ -6842,13 +6664,11 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>1</v>
-      </c>
-      <c r="K28" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="25.5" hidden="1" customHeight="1">
+        <f t="shared" ref="J28:J38" si="2">COUNTIF(E28:I28,(NOT(FALSE)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="25.5" hidden="1" customHeight="1">
       <c r="A29" t="s">
         <v>374</v>
       </c>
@@ -6877,13 +6697,11 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="25.5" hidden="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="25.5" hidden="1">
       <c r="A30" t="s">
         <v>374</v>
       </c>
@@ -6912,13 +6730,11 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="38.25" hidden="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="38.25" hidden="1">
       <c r="A31" t="s">
         <v>373</v>
       </c>
@@ -6947,13 +6763,11 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="51" hidden="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="51" hidden="1">
       <c r="A32" t="s">
         <v>374</v>
       </c>
@@ -6982,10 +6796,8 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32" t="s">
-        <v>440</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="25.5" hidden="1">
@@ -7017,10 +6829,8 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33" t="s">
-        <v>439</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="51" hidden="1" customHeight="1">
@@ -7050,10 +6860,8 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34" t="s">
-        <v>438</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="25.5" hidden="1" customHeight="1">
@@ -7085,10 +6893,8 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35" t="s">
-        <v>437</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="25.5" hidden="1" customHeight="1">
@@ -7120,10 +6926,8 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36" t="s">
-        <v>436</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="25.5" hidden="1">
@@ -7155,10 +6959,8 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37" t="s">
-        <v>435</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="25.5" hidden="1">
@@ -7190,14 +6992,12 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38" t="s">
-        <v>434</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11" hidden="1">
-      <c r="A39" s="60"/>
+      <c r="A39" s="59"/>
       <c r="C39" s="21" t="s">
         <v>105</v>
       </c>
@@ -7207,14 +7007,11 @@
       <c r="G39" s="33"/>
       <c r="H39" s="33"/>
       <c r="I39" s="33"/>
-      <c r="J39">
-        <v>1</v>
-      </c>
-      <c r="K39" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="25.5">
+      <c r="J39" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="25.5" hidden="1">
       <c r="A40" t="s">
         <v>375</v>
       </c>
@@ -7243,13 +7040,11 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>1</v>
-      </c>
-      <c r="K40" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="15" customHeight="1">
+        <f t="shared" ref="J40:J43" si="3">COUNTIF(E40:I40,(NOT(FALSE)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="15" hidden="1" customHeight="1">
       <c r="A41" t="s">
         <v>375</v>
       </c>
@@ -7276,13 +7071,11 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>2</v>
-      </c>
-      <c r="K41" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="15" customHeight="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="15" hidden="1" customHeight="1">
       <c r="A42" t="s">
         <v>375</v>
       </c>
@@ -7309,13 +7102,11 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>2</v>
-      </c>
-      <c r="K42" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="25.5" customHeight="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="25.5" hidden="1" customHeight="1">
       <c r="A43" t="s">
         <v>375</v>
       </c>
@@ -7342,14 +7133,12 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>1</v>
-      </c>
-      <c r="K43" t="s">
-        <v>430</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11" hidden="1">
-      <c r="A44" s="60"/>
+      <c r="A44" s="59"/>
       <c r="C44" s="21" t="s">
         <v>115</v>
       </c>
@@ -7359,11 +7148,8 @@
       <c r="G44" s="33"/>
       <c r="H44" s="33"/>
       <c r="I44" s="33"/>
-      <c r="J44">
-        <v>1</v>
-      </c>
-      <c r="K44" t="s">
-        <v>424</v>
+      <c r="J44" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="25.5" hidden="1">
@@ -7395,10 +7181,11 @@
         <v>0</v>
       </c>
       <c r="J45">
+        <f t="shared" ref="J45:J47" si="4">COUNTIF(E45:I45,(NOT(FALSE)))</f>
         <v>2</v>
       </c>
       <c r="K45" t="s">
-        <v>429</v>
+        <v>387</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="25.5" hidden="1">
@@ -7430,10 +7217,8 @@
         <v>0</v>
       </c>
       <c r="J46">
+        <f t="shared" si="4"/>
         <v>2</v>
-      </c>
-      <c r="K46" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="25.5" hidden="1" customHeight="1">
@@ -7463,10 +7248,8 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>1</v>
-      </c>
-      <c r="K47" t="s">
-        <v>427</v>
+        <f t="shared" si="4"/>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="25.5" hidden="1">
@@ -7498,13 +7281,14 @@
         <v>0</v>
       </c>
       <c r="J48">
+        <f t="shared" ref="J48:J50" si="5">COUNTIF(E48:I48,(NOT(FALSE)))</f>
         <v>2</v>
       </c>
       <c r="K48" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="38.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="38.25" hidden="1">
       <c r="A49" t="s">
         <v>375</v>
       </c>
@@ -7533,10 +7317,8 @@
         <v>0</v>
       </c>
       <c r="J49">
-        <v>1</v>
-      </c>
-      <c r="K49" t="s">
-        <v>424</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="51" hidden="1">
@@ -7568,14 +7350,12 @@
         <v>0</v>
       </c>
       <c r="J50">
-        <v>1</v>
-      </c>
-      <c r="K50" t="s">
-        <v>425</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11" hidden="1">
-      <c r="A51" s="60"/>
+      <c r="A51" s="59"/>
       <c r="C51" s="22" t="s">
         <v>135</v>
       </c>
@@ -7625,7 +7405,7 @@
       </c>
     </row>
     <row r="53" spans="1:11" hidden="1">
-      <c r="A53" s="60"/>
+      <c r="A53" s="59"/>
       <c r="C53" s="22" t="s">
         <v>137</v>
       </c>
@@ -7639,7 +7419,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="25.5">
+    <row r="54" spans="1:11" ht="25.5" hidden="1">
       <c r="A54" t="s">
         <v>375</v>
       </c>
@@ -7676,7 +7456,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" hidden="1">
-      <c r="A55" s="60"/>
+      <c r="A55" s="59"/>
       <c r="C55" s="22" t="s">
         <v>139</v>
       </c>
@@ -7690,7 +7470,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="25.5">
+    <row r="56" spans="1:11" ht="25.5" hidden="1">
       <c r="A56" t="s">
         <v>375</v>
       </c>
@@ -7719,7 +7499,7 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <f t="shared" ref="J56:J59" si="0">COUNTIF(E56:I56,(NOT(FALSE)))</f>
+        <f t="shared" ref="J56:J59" si="6">COUNTIF(E56:I56,(NOT(FALSE)))</f>
         <v>0</v>
       </c>
       <c r="K56" t="s">
@@ -7755,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="J57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
@@ -7788,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="J58">
-        <f t="shared" ref="J58" si="1">COUNTIF(E58:I58,(NOT(FALSE)))</f>
+        <f t="shared" ref="J58" si="7">COUNTIF(E58:I58,(NOT(FALSE)))</f>
         <v>0</v>
       </c>
     </row>
@@ -7821,12 +7601,12 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11" hidden="1">
-      <c r="A60" s="60"/>
+      <c r="A60" s="59"/>
       <c r="C60" s="22" t="s">
         <v>148</v>
       </c>
@@ -7869,7 +7649,7 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <f t="shared" ref="J61:J62" si="2">COUNTIF(E61:I61,(NOT(FALSE)))</f>
+        <f t="shared" ref="J61:J62" si="8">COUNTIF(E61:I61,(NOT(FALSE)))</f>
         <v>0</v>
       </c>
     </row>
@@ -7902,12 +7682,12 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11" hidden="1">
-      <c r="A63" s="60"/>
+      <c r="A63" s="59"/>
       <c r="C63" s="22" t="s">
         <v>153</v>
       </c>
@@ -7950,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <f t="shared" ref="J64:J65" si="3">COUNTIF(E64:I64,(NOT(FALSE)))</f>
+        <f t="shared" ref="J64:J65" si="9">COUNTIF(E64:I64,(NOT(FALSE)))</f>
         <v>0</v>
       </c>
     </row>
@@ -7983,12 +7763,12 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="30" hidden="1">
-      <c r="A66" s="60"/>
+      <c r="A66" s="59"/>
       <c r="C66" s="23" t="s">
         <v>158</v>
       </c>
@@ -8004,7 +7784,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="30" hidden="1">
+    <row r="67" spans="1:11" ht="30">
       <c r="A67" t="s">
         <v>369</v>
       </c>
@@ -8033,11 +7813,11 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <f t="shared" ref="J67:J80" si="4">COUNTIF(E67:I67,(NOT(FALSE)))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="45" hidden="1">
+        <f t="shared" ref="J67:J80" si="10">COUNTIF(E67:I67,(NOT(FALSE)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="45">
       <c r="A68" t="s">
         <v>369</v>
       </c>
@@ -8066,11 +7846,11 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="30" hidden="1">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="30">
       <c r="A69" t="s">
         <v>369</v>
       </c>
@@ -8099,14 +7879,14 @@
         <v>0</v>
       </c>
       <c r="J69">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K69" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="45" hidden="1">
+    <row r="70" spans="1:11" ht="45">
       <c r="A70" t="s">
         <v>369</v>
       </c>
@@ -8135,14 +7915,14 @@
         <v>0</v>
       </c>
       <c r="J70">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K70" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="75" hidden="1">
+    <row r="71" spans="1:11" ht="75">
       <c r="A71" t="s">
         <v>369</v>
       </c>
@@ -8171,14 +7951,14 @@
         <v>0</v>
       </c>
       <c r="J71">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K71" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="30" hidden="1">
+    <row r="72" spans="1:11" ht="30">
       <c r="A72" t="s">
         <v>369</v>
       </c>
@@ -8207,14 +7987,14 @@
         <v>0</v>
       </c>
       <c r="J72">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K72" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="30" hidden="1">
+    <row r="73" spans="1:11" ht="30">
       <c r="A73" t="s">
         <v>369</v>
       </c>
@@ -8243,14 +8023,14 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K73" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1">
+    <row r="74" spans="1:11">
       <c r="A74" t="s">
         <v>369</v>
       </c>
@@ -8267,7 +8047,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="45" hidden="1">
+    <row r="75" spans="1:11" ht="45">
       <c r="A75" t="s">
         <v>369</v>
       </c>
@@ -8296,11 +8076,11 @@
         <v>0</v>
       </c>
       <c r="J75">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="45" hidden="1">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="45">
       <c r="A76" t="s">
         <v>369</v>
       </c>
@@ -8329,11 +8109,11 @@
         <v>0</v>
       </c>
       <c r="J76">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="45" hidden="1">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="45">
       <c r="A77" t="s">
         <v>369</v>
       </c>
@@ -8362,14 +8142,14 @@
         <v>0</v>
       </c>
       <c r="J77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K77" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="45" hidden="1">
+    <row r="78" spans="1:11" ht="45">
       <c r="A78" t="s">
         <v>369</v>
       </c>
@@ -8398,11 +8178,11 @@
         <v>0</v>
       </c>
       <c r="J78">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="30" hidden="1">
+    <row r="79" spans="1:11" ht="30">
       <c r="A79" t="s">
         <v>369</v>
       </c>
@@ -8431,14 +8211,14 @@
         <v>0</v>
       </c>
       <c r="J79">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K79" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="30" hidden="1">
+    <row r="80" spans="1:11" ht="30">
       <c r="A80" t="s">
         <v>369</v>
       </c>
@@ -8467,7 +8247,7 @@
         <v>0</v>
       </c>
       <c r="J80">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K80" t="s">
@@ -8475,7 +8255,7 @@
       </c>
     </row>
     <row r="81" spans="1:11" hidden="1">
-      <c r="A81" s="60"/>
+      <c r="A81" s="59"/>
       <c r="C81" s="23" t="s">
         <v>186</v>
       </c>
@@ -8489,7 +8269,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="30" hidden="1">
+    <row r="82" spans="1:11" ht="30">
       <c r="A82" t="s">
         <v>369</v>
       </c>
@@ -8526,7 +8306,7 @@
       </c>
     </row>
     <row r="83" spans="1:11" hidden="1">
-      <c r="A83" s="60"/>
+      <c r="A83" s="59"/>
       <c r="C83" s="23" t="s">
         <v>189</v>
       </c>
@@ -8540,7 +8320,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="30" hidden="1">
+    <row r="84" spans="1:11" ht="30">
       <c r="A84" t="s">
         <v>369</v>
       </c>
@@ -8569,14 +8349,14 @@
         <v>0</v>
       </c>
       <c r="J84">
-        <f t="shared" ref="J84:J85" si="5">COUNTIF(E84:I84,(NOT(FALSE)))</f>
+        <f t="shared" ref="J84:J85" si="11">COUNTIF(E84:I84,(NOT(FALSE)))</f>
         <v>1</v>
       </c>
       <c r="K84" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="30" hidden="1">
+    <row r="85" spans="1:11" ht="30">
       <c r="A85" t="s">
         <v>369</v>
       </c>
@@ -8605,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="J85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="K85" t="s">
@@ -8613,7 +8393,7 @@
       </c>
     </row>
     <row r="86" spans="1:11" ht="30" hidden="1">
-      <c r="A86" s="60"/>
+      <c r="A86" s="59"/>
       <c r="C86" s="24" t="s">
         <v>278</v>
       </c>
@@ -8629,7 +8409,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="15" hidden="1" customHeight="1">
+    <row r="87" spans="1:11" ht="15" customHeight="1">
       <c r="A87" t="s">
         <v>369</v>
       </c>
@@ -8662,7 +8442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1">
+    <row r="88" spans="1:11">
       <c r="A88" t="s">
         <v>369</v>
       </c>
@@ -8687,11 +8467,11 @@
         <v>0</v>
       </c>
       <c r="J88">
-        <f t="shared" ref="J88:J121" si="6">COUNTIF(E88:I88,(NOT(FALSE)))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" hidden="1">
+        <f t="shared" ref="J88:J121" si="12">COUNTIF(E88:I88,(NOT(FALSE)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
       <c r="A89" t="s">
         <v>369</v>
       </c>
@@ -8716,11 +8496,11 @@
         <v>0</v>
       </c>
       <c r="J89">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
       <c r="A90" t="s">
         <v>369</v>
       </c>
@@ -8745,11 +8525,11 @@
         <v>0</v>
       </c>
       <c r="J90">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="30" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="30">
       <c r="A91" t="s">
         <v>369</v>
       </c>
@@ -8774,11 +8554,11 @@
         <v>0</v>
       </c>
       <c r="J91">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
       <c r="A92" t="s">
         <v>369</v>
       </c>
@@ -8803,14 +8583,14 @@
         <v>0</v>
       </c>
       <c r="J92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K92" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="15" hidden="1" customHeight="1">
+    <row r="93" spans="1:11" ht="15" customHeight="1">
       <c r="A93" t="s">
         <v>369</v>
       </c>
@@ -8839,11 +8619,11 @@
         <v>0</v>
       </c>
       <c r="J93">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="30" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="30">
       <c r="A94" t="s">
         <v>369</v>
       </c>
@@ -8868,11 +8648,11 @@
         <v>0</v>
       </c>
       <c r="J94">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" ht="30" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="30">
       <c r="A95" t="s">
         <v>369</v>
       </c>
@@ -8897,14 +8677,14 @@
         <v>0</v>
       </c>
       <c r="J95">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K95" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="30" hidden="1">
+    <row r="96" spans="1:11" ht="30">
       <c r="A96" t="s">
         <v>369</v>
       </c>
@@ -8929,14 +8709,14 @@
         <v>0</v>
       </c>
       <c r="J96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K96" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="30" hidden="1">
+    <row r="97" spans="1:11" ht="30">
       <c r="A97" t="s">
         <v>369</v>
       </c>
@@ -8961,14 +8741,14 @@
         <v>0</v>
       </c>
       <c r="J97">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K97" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="15" hidden="1" customHeight="1">
+    <row r="98" spans="1:11" ht="15" customHeight="1">
       <c r="A98" t="s">
         <v>369</v>
       </c>
@@ -8997,11 +8777,11 @@
         <v>0</v>
       </c>
       <c r="J98">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="30" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="30">
       <c r="A99" t="s">
         <v>369</v>
       </c>
@@ -9026,11 +8806,11 @@
         <v>0</v>
       </c>
       <c r="J99">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
       <c r="A100" t="s">
         <v>369</v>
       </c>
@@ -9055,14 +8835,14 @@
         <v>0</v>
       </c>
       <c r="J100">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K100" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1">
+    <row r="101" spans="1:11">
       <c r="A101" t="s">
         <v>369</v>
       </c>
@@ -9087,11 +8867,11 @@
         <v>0</v>
       </c>
       <c r="J101">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" ht="30" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="30">
       <c r="A102" t="s">
         <v>369</v>
       </c>
@@ -9116,14 +8896,14 @@
         <v>0</v>
       </c>
       <c r="J102">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K102" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1">
+    <row r="103" spans="1:11">
       <c r="A103" t="s">
         <v>369</v>
       </c>
@@ -9148,11 +8928,11 @@
         <v>0</v>
       </c>
       <c r="J103">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" ht="30" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="30">
       <c r="A104" t="s">
         <v>369</v>
       </c>
@@ -9177,14 +8957,14 @@
         <v>0</v>
       </c>
       <c r="J104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K104" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1">
+    <row r="105" spans="1:11">
       <c r="A105" t="s">
         <v>369</v>
       </c>
@@ -9209,14 +8989,14 @@
         <v>0</v>
       </c>
       <c r="J105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K105" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="30" hidden="1">
+    <row r="106" spans="1:11" ht="30">
       <c r="A106" t="s">
         <v>369</v>
       </c>
@@ -9241,11 +9021,11 @@
         <v>0</v>
       </c>
       <c r="J106">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" ht="30" hidden="1" customHeight="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="30" customHeight="1">
       <c r="A107" t="s">
         <v>369</v>
       </c>
@@ -9274,14 +9054,14 @@
         <v>0</v>
       </c>
       <c r="J107">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K107" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="30" hidden="1">
+    <row r="108" spans="1:11" ht="30">
       <c r="A108" t="s">
         <v>369</v>
       </c>
@@ -9306,14 +9086,14 @@
         <v>0</v>
       </c>
       <c r="J108">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K108" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="30" hidden="1">
+    <row r="109" spans="1:11" ht="30">
       <c r="A109" t="s">
         <v>369</v>
       </c>
@@ -9338,14 +9118,14 @@
         <v>0</v>
       </c>
       <c r="J109">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K109" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="110" spans="1:11" hidden="1">
+    <row r="110" spans="1:11">
       <c r="A110" t="s">
         <v>369</v>
       </c>
@@ -9370,11 +9150,11 @@
         <v>0</v>
       </c>
       <c r="J110">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" ht="30" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="30">
       <c r="A111" t="s">
         <v>369</v>
       </c>
@@ -9399,11 +9179,11 @@
         <v>0</v>
       </c>
       <c r="J111">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" ht="45" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="45">
       <c r="A112" t="s">
         <v>369</v>
       </c>
@@ -9428,14 +9208,14 @@
         <v>0</v>
       </c>
       <c r="J112">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K112" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="60" hidden="1">
+    <row r="113" spans="1:11" ht="60">
       <c r="A113" t="s">
         <v>369</v>
       </c>
@@ -9460,11 +9240,11 @@
         <v>0</v>
       </c>
       <c r="J113">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" ht="30" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="30">
       <c r="A114" t="s">
         <v>369</v>
       </c>
@@ -9489,14 +9269,14 @@
         <v>0</v>
       </c>
       <c r="J114">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K114" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="15" hidden="1" customHeight="1">
+    <row r="115" spans="1:11" ht="15" customHeight="1">
       <c r="A115" t="s">
         <v>369</v>
       </c>
@@ -9525,11 +9305,11 @@
         <v>0</v>
       </c>
       <c r="J115">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" ht="30" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="30">
       <c r="A116" t="s">
         <v>369</v>
       </c>
@@ -9554,11 +9334,11 @@
         <v>0</v>
       </c>
       <c r="J116">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="45" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="45">
       <c r="A117" t="s">
         <v>369</v>
       </c>
@@ -9583,14 +9363,14 @@
         <v>0</v>
       </c>
       <c r="J117">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K117" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="30" hidden="1">
+    <row r="118" spans="1:11" ht="30">
       <c r="A118" t="s">
         <v>369</v>
       </c>
@@ -9619,11 +9399,11 @@
         <v>0</v>
       </c>
       <c r="J118">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" ht="30" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="30">
       <c r="A119" t="s">
         <v>369</v>
       </c>
@@ -9648,11 +9428,11 @@
         <v>0</v>
       </c>
       <c r="J119">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" ht="45" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="45">
       <c r="A120" t="s">
         <v>369</v>
       </c>
@@ -9677,11 +9457,11 @@
         <v>0</v>
       </c>
       <c r="J120">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" hidden="1">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
       <c r="A121" t="s">
         <v>369</v>
       </c>
@@ -9706,7 +9486,7 @@
         <v>0</v>
       </c>
       <c r="J121">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K121" t="s">
@@ -9714,7 +9494,7 @@
       </c>
     </row>
     <row r="122" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A122" s="60"/>
+      <c r="A122" s="59"/>
       <c r="B122" s="30" t="s">
         <v>279</v>
       </c>
@@ -9742,23 +9522,23 @@
         <v>380</v>
       </c>
       <c r="E123" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F123" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I123" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123">
         <f>COUNTIF(E123:I123,(NOT(FALSE)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="12.75" hidden="1" customHeight="1">
@@ -9790,7 +9570,7 @@
         <v>0</v>
       </c>
       <c r="J124">
-        <f t="shared" ref="J124:J155" si="7">COUNTIF(E124:I124,(NOT(FALSE)))</f>
+        <f t="shared" ref="J124:J155" si="13">COUNTIF(E124:I124,(NOT(FALSE)))</f>
         <v>2</v>
       </c>
     </row>
@@ -9823,7 +9603,7 @@
         <v>1</v>
       </c>
       <c r="J125">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="K125" t="s">
@@ -9859,7 +9639,7 @@
         <v>0</v>
       </c>
       <c r="J126">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="K126" t="s">
@@ -9912,7 +9692,7 @@
         <v>1</v>
       </c>
       <c r="J128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="K128" t="s">
@@ -9948,7 +9728,7 @@
         <v>1</v>
       </c>
       <c r="J129">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="K129" t="s">
@@ -9984,7 +9764,7 @@
         <v>0</v>
       </c>
       <c r="J130">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="K130" t="s">
@@ -10037,7 +9817,7 @@
         <v>0</v>
       </c>
       <c r="J132">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="K132" t="s">
@@ -10073,7 +9853,7 @@
         <v>0</v>
       </c>
       <c r="J133">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="K133" t="s">
@@ -10090,8 +9870,8 @@
       <c r="C134" s="54" t="s">
         <v>306</v>
       </c>
-      <c r="D134" s="55" t="s">
-        <v>387</v>
+      <c r="D134" t="s">
+        <v>424</v>
       </c>
       <c r="E134" s="3" t="b">
         <v>1</v>
@@ -10109,7 +9889,7 @@
         <v>0</v>
       </c>
       <c r="J134">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="K134" t="s">
@@ -10143,7 +9923,7 @@
       <c r="C136" s="54">
         <v>6</v>
       </c>
-      <c r="D136" s="27" t="s">
+      <c r="D136" s="64" t="s">
         <v>308</v>
       </c>
       <c r="E136" s="3" t="b">
@@ -10162,7 +9942,7 @@
         <v>1</v>
       </c>
       <c r="J136">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
     </row>
@@ -10176,7 +9956,7 @@
       <c r="C137" s="54">
         <v>7</v>
       </c>
-      <c r="D137" s="27" t="s">
+      <c r="D137" s="64" t="s">
         <v>310</v>
       </c>
       <c r="E137" s="3" t="b">
@@ -10195,12 +9975,12 @@
         <v>1</v>
       </c>
       <c r="J137">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:11" hidden="1">
-      <c r="A138" s="60"/>
+      <c r="A138" s="59"/>
       <c r="C138" s="51" t="s">
         <v>10</v>
       </c>
@@ -10243,7 +10023,7 @@
         <v>1</v>
       </c>
       <c r="J139">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
     </row>
@@ -10276,7 +10056,7 @@
         <v>0</v>
       </c>
       <c r="J140">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
     </row>
@@ -10309,12 +10089,12 @@
         <v>0</v>
       </c>
       <c r="J141">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="15" hidden="1" customHeight="1">
-      <c r="A142" s="60"/>
+      <c r="A142" s="59"/>
       <c r="C142" s="51" t="s">
         <v>163</v>
       </c>
@@ -10357,7 +10137,7 @@
         <v>0</v>
       </c>
       <c r="J143">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
     </row>
@@ -10390,7 +10170,7 @@
         <v>0</v>
       </c>
       <c r="J144">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
     </row>
@@ -10423,7 +10203,7 @@
         <v>0</v>
       </c>
       <c r="J145">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
     </row>
@@ -10456,7 +10236,7 @@
         <v>0</v>
       </c>
       <c r="J146">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
     </row>
@@ -10489,7 +10269,7 @@
         <v>0</v>
       </c>
       <c r="J147">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="K147" t="s">
@@ -10525,12 +10305,12 @@
         <v>0</v>
       </c>
       <c r="J148">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:11" hidden="1">
-      <c r="A149" s="60"/>
+      <c r="A149" s="59"/>
       <c r="C149" s="51" t="s">
         <v>332</v>
       </c>
@@ -10573,7 +10353,7 @@
         <v>0</v>
       </c>
       <c r="J150">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -10604,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="J151">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -10635,7 +10415,7 @@
         <v>0</v>
       </c>
       <c r="J152">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="K152" t="s">
@@ -10669,7 +10449,7 @@
         <v>0</v>
       </c>
       <c r="J153">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="K153" t="s">
@@ -10705,7 +10485,7 @@
         <v>0</v>
       </c>
       <c r="J154">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -10738,12 +10518,12 @@
         <v>0</v>
       </c>
       <c r="J155">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="18" customHeight="1">
-      <c r="B156" s="61"/>
+      <c r="B156" s="60"/>
     </row>
     <row r="157" spans="1:11" ht="18" customHeight="1"/>
     <row r="158" spans="1:11" ht="18" customHeight="1"/>
@@ -10783,13 +10563,8 @@
   <autoFilter ref="A1:K155" xr:uid="{7648BC2A-312E-453A-BBA9-B96484F08716}">
     <filterColumn colId="0">
       <filters>
-        <filter val="9 Redacción"/>
+        <filter val="3 Estrategia de búsqueda"/>
       </filters>
-    </filterColumn>
-    <filterColumn colId="10">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="J3 J5 J7:J8 J10:J26 J28:J38 J40:J43 J45:J50 J52 J54 J56:J59 J61:J62 J64:J65 J67:J80 J82 J84:J85 J87:J126 J128:J130 J132:J134 J136:J155">
@@ -10901,14 +10676,14 @@
       <c r="E9" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="56" t="s">
+      <c r="F9" s="55" t="s">
         <v>271</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
     </row>
     <row r="10" spans="3:14">
       <c r="C10" s="2" t="s">
@@ -11086,7 +10861,7 @@
       <c r="E22" s="40" t="s">
         <v>241</v>
       </c>
-      <c r="F22" s="57" t="s">
+      <c r="F22" s="56" t="s">
         <v>354</v>
       </c>
       <c r="G22">
@@ -11104,7 +10879,7 @@
       <c r="E23" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="F23" s="57" t="s">
+      <c r="F23" s="56" t="s">
         <v>354</v>
       </c>
     </row>
@@ -11118,7 +10893,7 @@
       <c r="E24" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="F24" s="57" t="s">
+      <c r="F24" s="56" t="s">
         <v>354</v>
       </c>
     </row>
@@ -11132,7 +10907,7 @@
       <c r="E25" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F25" s="58" t="s">
+      <c r="F25" s="57" t="s">
         <v>273</v>
       </c>
     </row>
@@ -11141,14 +10916,12 @@
         <v>46280</v>
       </c>
       <c r="D26" s="40" t="s">
-        <v>273</v>
+        <v>371</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>465</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>466</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="F26" s="4"/>
     </row>
     <row r="27" spans="3:8">
       <c r="C27" s="39">
